--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 09:15:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 10:40:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 10:40:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-10 10:40:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-10 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,156 +1403,6513 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kokand-1912</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Al-Nahda</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Al Seeb</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:55:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sogdiana</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1</v>
+      </c>
+      <c r="AN9">
+        <v>-1</v>
+      </c>
+      <c r="AO9">
+        <v>-1</v>
+      </c>
+      <c r="AP9">
+        <v>-1</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Georgia Erovnuli Liga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dinamo Tbilisi</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Meshakhte</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-1</v>
+      </c>
+      <c r="AN10">
+        <v>-1</v>
+      </c>
+      <c r="AO10">
+        <v>-1</v>
+      </c>
+      <c r="AP10">
+        <v>-1</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shams Azar Qazvin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gol Gohar</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-1</v>
+      </c>
+      <c r="AN11">
+        <v>-1</v>
+      </c>
+      <c r="AO11">
+        <v>-1</v>
+      </c>
+      <c r="AP11">
+        <v>-1</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Esteghlal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paykan</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Esteghlal Khuzestan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tractor Sazi</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Maccabi Kabilio Jaffa</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hapoel Ra'anana</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Saba</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Maccabi Kiryat Gat</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ironi Modi'in FC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bnei Yehuda</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hapoel Afula</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Shalem</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Maccabi Ahi Nazareth</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hapoel Rishon LeZion</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kiryat Yam SC</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Smail</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fanja</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Latvia Virsliga</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Super Nova</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tukums</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UAE Arabian Gulf League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al Ain</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Al Wasl</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>2.5</v>
+      </c>
+      <c r="O24">
+        <v>3.5</v>
+      </c>
+      <c r="P24">
+        <v>2.74</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>1.9</v>
+      </c>
+      <c r="AB24">
+        <v>1.9</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Georgia Erovnuli Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gagra</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Torpedo Kutaisi</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Östersunds FK</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brage</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Öster</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bokelj</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Otrant-Olympic</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Budućnost</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FK Jezero Plav</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Montenegro Montenegrin First League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Arsenal Tivat</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mladost DG</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cannes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Amiens SC</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>1.1</v>
+      </c>
+      <c r="O37">
+        <v>11.5</v>
+      </c>
+      <c r="P37">
+        <v>20.17</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>1.28</v>
+      </c>
+      <c r="AB37">
+        <v>3.75</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Slavia Praha</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JS El Biar</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Luton Town</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>2026-09-10 21:30:00</t>
         </is>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G7">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G30">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G35">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G38">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G7">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G7">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>20.17</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>20.17</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G38">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU46"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-10 11:55:00</t>
+          <t>2026-09-10 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-10 12:00:00</t>
+          <t>2026-09-10 11:55:00</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-10 12:30:00</t>
+          <t>2026-09-10 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-10 13:00:00</t>
+          <t>2026-09-10 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fanja</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fanja</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-10 13:15:00</t>
+          <t>2026-09-10 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-10 13:45:00</t>
+          <t>2026-09-10 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-10 13:45:00</t>
+          <t>2026-09-10 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-10 15:45:00</t>
+          <t>2026-09-10 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>20.17</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>7.53</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>20.17</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G41">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-10 16:15:00</t>
+          <t>2026-09-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-10 20:00:00</t>
+          <t>2026-09-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,156 +7760,808 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
-      </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>0</v>
-      </c>
-      <c r="AG46">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>0</v>
-      </c>
-      <c r="AK46">
-        <v>0</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>-1</v>
-      </c>
-      <c r="AN46">
-        <v>-1</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>-1</v>
-      </c>
-      <c r="AQ46">
-        <v>0</v>
-      </c>
-      <c r="AR46">
-        <v>0</v>
-      </c>
-      <c r="AS46">
-        <v>0</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-10 21:30:00</t>
         </is>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>7.53</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>7.53</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00:00</t>
+          <t>2026-09-10 14:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1622,55 +1622,55 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>10.33</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G33">

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>2.74</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA27">
         <v>1.9</v>
@@ -4755,19 +4755,19 @@
         <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4393,55 +4393,55 @@
         <v>1.17</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G20">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>2.19</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>20.17</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA39">
         <v>1.28</v>
@@ -6711,19 +6711,19 @@
         <v>3.75</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q49">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1646,16 +1646,16 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>4.4</v>
+        <v>4.63</v>
       </c>
       <c r="AA8">
         <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC8">
         <v>2.46</v>
@@ -1664,10 +1664,10 @@
         <v>1.52</v>
       </c>
       <c r="AE8">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
         <v>2.45</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="O25">
-        <v>6.99</v>
+        <v>6.5</v>
       </c>
       <c r="P25">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Q25">
-        <v>7.35</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="S25">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T25">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="U25">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V25">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="W25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB25">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="AC25">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD25">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE25">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AF25">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AG25">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>3.6</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
         <v>1.05</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>20.17</v>
+        <v>2.35</v>
       </c>
       <c r="Q39">
+        <v>3.3</v>
+      </c>
+      <c r="R39">
+        <v>2.13</v>
+      </c>
+      <c r="S39">
+        <v>1.37</v>
+      </c>
+      <c r="T39">
+        <v>3.08</v>
+      </c>
+      <c r="U39">
+        <v>2.63</v>
+      </c>
+      <c r="V39">
         <v>1.48</v>
       </c>
-      <c r="R39">
-        <v>2.97</v>
-      </c>
-      <c r="S39">
-        <v>1.21</v>
-      </c>
-      <c r="T39">
-        <v>4.2</v>
-      </c>
-      <c r="U39">
-        <v>1.73</v>
-      </c>
-      <c r="V39">
-        <v>1.95</v>
-      </c>
       <c r="W39">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>7.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA39">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="AB39">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>1.72</v>
+        <v>2.84</v>
       </c>
       <c r="AD39">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>5.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.15</v>
+      </c>
+      <c r="O40">
+        <v>3.65</v>
+      </c>
+      <c r="P40">
+        <v>3.2</v>
+      </c>
+      <c r="Q40">
+        <v>2.55</v>
+      </c>
+      <c r="R40">
+        <v>2.21</v>
+      </c>
+      <c r="S40">
+        <v>1.29</v>
+      </c>
+      <c r="T40">
+        <v>3.05</v>
+      </c>
+      <c r="U40">
+        <v>2.4</v>
+      </c>
+      <c r="V40">
+        <v>1.6</v>
+      </c>
+      <c r="W40">
         <v>1.12</v>
       </c>
-      <c r="O40">
-        <v>10</v>
-      </c>
-      <c r="P40">
-        <v>12</v>
-      </c>
-      <c r="Q40">
-        <v>1.36</v>
-      </c>
-      <c r="R40">
-        <v>3.74</v>
-      </c>
-      <c r="S40">
-        <v>1.1</v>
-      </c>
-      <c r="T40">
-        <v>7.1</v>
-      </c>
-      <c r="U40">
-        <v>1.46</v>
-      </c>
-      <c r="V40">
-        <v>2.45</v>
-      </c>
-      <c r="W40">
-        <v>1.46</v>
-      </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>8.699999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="AA40">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC40">
-        <v>1.39</v>
+        <v>2.65</v>
       </c>
       <c r="AD40">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="AE40">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>6.3</v>
+        <v>1.71</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="P41">
+        <v>12</v>
+      </c>
+      <c r="Q41">
+        <v>1.36</v>
+      </c>
+      <c r="R41">
+        <v>3.74</v>
+      </c>
+      <c r="S41">
+        <v>1.1</v>
+      </c>
+      <c r="T41">
+        <v>7.1</v>
+      </c>
+      <c r="U41">
+        <v>1.46</v>
+      </c>
+      <c r="V41">
+        <v>2.45</v>
+      </c>
+      <c r="W41">
+        <v>1.46</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.01</v>
+      </c>
+      <c r="Z41">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA41">
+        <v>1.12</v>
+      </c>
+      <c r="AB41">
+        <v>4.75</v>
+      </c>
+      <c r="AC41">
+        <v>1.39</v>
+      </c>
+      <c r="AD41">
+        <v>2.72</v>
+      </c>
+      <c r="AE41">
+        <v>1.8</v>
+      </c>
+      <c r="AF41">
+        <v>1.55</v>
+      </c>
+      <c r="AG41">
         <v>2.35</v>
       </c>
-      <c r="Q41">
-        <v>3.3</v>
-      </c>
-      <c r="R41">
-        <v>2.13</v>
-      </c>
-      <c r="S41">
-        <v>1.37</v>
-      </c>
-      <c r="T41">
-        <v>3.08</v>
-      </c>
-      <c r="U41">
-        <v>2.63</v>
-      </c>
-      <c r="V41">
-        <v>1.48</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.84</v>
-      </c>
-      <c r="AA41">
-        <v>1.72</v>
-      </c>
-      <c r="AB41">
-        <v>2.05</v>
-      </c>
-      <c r="AC41">
-        <v>2.84</v>
-      </c>
-      <c r="AD41">
-        <v>1.38</v>
-      </c>
-      <c r="AE41">
-        <v>1.09</v>
-      </c>
-      <c r="AF41">
-        <v>1.57</v>
-      </c>
-      <c r="AG41">
-        <v>2.25</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>6.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="O42">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="P42">
-        <v>3.2</v>
+        <v>20.17</v>
       </c>
       <c r="Q42">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="R42">
-        <v>2.21</v>
+        <v>2.97</v>
       </c>
       <c r="S42">
+        <v>1.21</v>
+      </c>
+      <c r="T42">
+        <v>4.2</v>
+      </c>
+      <c r="U42">
+        <v>1.73</v>
+      </c>
+      <c r="V42">
+        <v>1.95</v>
+      </c>
+      <c r="W42">
         <v>1.29</v>
       </c>
-      <c r="T42">
-        <v>3.05</v>
-      </c>
-      <c r="U42">
-        <v>2.4</v>
-      </c>
-      <c r="V42">
-        <v>1.6</v>
-      </c>
-      <c r="W42">
-        <v>1.12</v>
-      </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z42">
-        <v>4.55</v>
+        <v>7.2</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AB42">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="AC42">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD42">
-        <v>1.48</v>
+        <v>2.24</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AK42">
-        <v>1.71</v>
+        <v>5.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.95</v>
+        <v>4.72</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="Q46">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="R46">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U46">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V46">
         <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA46">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB46">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC46">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG46">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="O48">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P48">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="R48">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="S48">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="U48">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="V48">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z48">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AA48">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AB48">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AC48">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="AD48">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE48">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AG48">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3916,43 +3916,43 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q24">
         <v>2.14</v>
       </c>
       <c r="R24">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4242,22 +4242,22 @@
         <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
         <v>1.63</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>5.11</v>
+        <v>4.75</v>
       </c>
       <c r="AA24">
         <v>1.5</v>
@@ -4266,19 +4266,19 @@
         <v>2.53</v>
       </c>
       <c r="AC24">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4553,28 +4553,28 @@
         <v>4.8</v>
       </c>
       <c r="P26">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T26">
         <v>3.65</v>
       </c>
       <c r="U26">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
         <v>1.59</v>
       </c>
       <c r="W26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4586,19 +4586,19 @@
         <v>5.5</v>
       </c>
       <c r="AA26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
         <v>2.55</v>
       </c>
       <c r="AC26">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD26">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
@@ -4620,7 +4620,7 @@
         <v>1.11</v>
       </c>
       <c r="AK26">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
         <v>1.3</v>
@@ -4731,7 +4731,7 @@
         <v>3.05</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
         <v>1.42</v>
@@ -4749,10 +4749,10 @@
         <v>3.9</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC27">
         <v>3.1</v>
@@ -4761,7 +4761,7 @@
         <v>1.37</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
@@ -5045,7 +5045,7 @@
         <v>1.3</v>
       </c>
       <c r="Q29">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="R29">
         <v>2.7</v>
@@ -5057,10 +5057,10 @@
         <v>3.9</v>
       </c>
       <c r="U29">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
         <v>1.18</v>
@@ -5078,7 +5078,7 @@
         <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AC29">
         <v>2.38</v>
@@ -5090,7 +5090,7 @@
         <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG29">
         <v>1.8</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="Q31">
-        <v>4.09</v>
+        <v>3.72</v>
       </c>
       <c r="R31">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T31">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V31">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB31">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC31">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD31">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG31">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O33">
         <v>3.8</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q33">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="R33">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U33">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
         <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z33">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="AA33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC33">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD33">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG33">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O37">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="P37">
-        <v>10.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q37">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R37">
         <v>2.4</v>
@@ -6358,46 +6358,46 @@
         <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA37">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AC37">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AG37">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
         <v>3.5</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="O38">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
@@ -6693,25 +6693,25 @@
         <v>1.48</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB39">
         <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AD39">
         <v>1.38</v>
@@ -6720,10 +6720,10 @@
         <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>2.55</v>
       </c>
       <c r="R40">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
         <v>1.29</v>
@@ -6853,7 +6853,7 @@
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
         <v>1.12</v>
@@ -6865,13 +6865,13 @@
         <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AB40">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AC40">
         <v>2.65</v>
@@ -6883,7 +6883,7 @@
         <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
         <v>2.3</v>
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P41">
         <v>12</v>
       </c>
       <c r="Q41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R41">
-        <v>3.74</v>
+        <v>3.86</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="T41">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V41">
         <v>2.45</v>
@@ -7031,16 +7031,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AA41">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB41">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AC41">
         <v>1.39</v>
       </c>
       <c r="AD41">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AE41">
         <v>1.8</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="O42">
-        <v>11.5</v>
+        <v>6.52</v>
       </c>
       <c r="P42">
-        <v>20.17</v>
+        <v>23.56</v>
       </c>
       <c r="Q42">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="R42">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="S42">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T42">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="U42">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V42">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="W42">
         <v>1.29</v>
@@ -7191,28 +7191,28 @@
         <v>1.03</v>
       </c>
       <c r="Z42">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AC42">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AD42">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AE42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF42">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.07</v>
       </c>
       <c r="AK42">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7647,61 +7647,61 @@
         <v>3.2</v>
       </c>
       <c r="O45">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="R45">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U45">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>3.43</v>
       </c>
       <c r="AA45">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB45">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC45">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE45">
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.57</v>
       </c>
       <c r="AK45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,58 +7970,58 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O47">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="R47">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S47">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="T47">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U47">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V47">
         <v>1.25</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
         <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="Z47">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AA47">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC47">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AD47">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>2.08</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O48">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q48">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U48">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V48">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
         <v>1.04</v>
@@ -8166,31 +8166,31 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB48">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC48">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AD48">
         <v>1.22</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R50">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB50">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD50">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AG50">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK50">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="Q5">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R5">
-        <v>2.48</v>
+        <v>2.71</v>
       </c>
       <c r="S5">
         <v>1.17</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
         <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB5">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AC5">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
+        <v>1.65</v>
+      </c>
+      <c r="AE5">
+        <v>1.26</v>
+      </c>
+      <c r="AF5">
         <v>1.59</v>
       </c>
-      <c r="AE5">
-        <v>1.2</v>
-      </c>
-      <c r="AF5">
-        <v>1.54</v>
-      </c>
       <c r="AG5">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1658,16 +1658,16 @@
         <v>2.3</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD8">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG8">
         <v>2.45</v>
@@ -3904,71 +3904,71 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U22">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
         <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
+        <v>1.22</v>
+      </c>
+      <c r="Z22">
+        <v>3.4</v>
+      </c>
+      <c r="AA22">
+        <v>1.78</v>
+      </c>
+      <c r="AB22">
+        <v>1.85</v>
+      </c>
+      <c r="AC22">
+        <v>2.95</v>
+      </c>
+      <c r="AD22">
+        <v>1.3</v>
+      </c>
+      <c r="AE22">
+        <v>1.07</v>
+      </c>
+      <c r="AF22">
+        <v>1.6</v>
+      </c>
+      <c r="AG22">
+        <v>2.07</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.24</v>
       </c>
-      <c r="Z22">
-        <v>3.5</v>
-      </c>
-      <c r="AA22">
-        <v>1.79</v>
-      </c>
-      <c r="AB22">
-        <v>1.91</v>
-      </c>
-      <c r="AC22">
-        <v>2.82</v>
-      </c>
-      <c r="AD22">
-        <v>1.34</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>1.7</v>
-      </c>
-      <c r="AG22">
-        <v>2.15</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4233,31 +4233,31 @@
         <v>2.14</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA24">
         <v>1.5</v>
@@ -4266,19 +4266,19 @@
         <v>2.53</v>
       </c>
       <c r="AC24">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD24">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK24">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,34 +4384,34 @@
         </is>
       </c>
       <c r="N25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="P25">
         <v>1.16</v>
       </c>
       <c r="Q25">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R25">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="S25">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="U25">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V25">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="W25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4420,10 +4420,10 @@
         <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="AA25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB25">
         <v>3.39</v>
@@ -4432,16 +4432,16 @@
         <v>1.82</v>
       </c>
       <c r="AD25">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE25">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AF25">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>7.53</v>
+        <v>11</v>
       </c>
       <c r="O29">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q29">
         <v>6.25</v>
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="O37">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="P37">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Q37">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V37">
         <v>1.44</v>
@@ -6373,28 +6373,28 @@
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB37">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC37">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AD37">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AG37">
         <v>1.57</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q38">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
         <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="AA38">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB38">
         <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="Q46">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S46">
         <v>1.38</v>
@@ -7828,43 +7828,43 @@
         <v>2.96</v>
       </c>
       <c r="U46">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
         <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="AA46">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AB46">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC46">
         <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>3.5</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -8317,10 +8317,10 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -8329,31 +8329,31 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4553,25 +4553,25 @@
         <v>4.8</v>
       </c>
       <c r="P26">
-        <v>6.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q26">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R26">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="S26">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T26">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W26">
         <v>1.17</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB26">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC26">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD26">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE26">
         <v>1.25</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.26</v>
+        <v>2.78</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="V27">
         <v>1.42</v>
@@ -4743,31 +4743,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
         <v>3.9</v>
       </c>
       <c r="AA27">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>11</v>
+        <v>7.53</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="P29">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q29">
         <v>6.25</v>
@@ -5066,7 +5066,7 @@
         <v>1.18</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.16</v>
@@ -5075,7 +5075,7 @@
         <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB29">
         <v>2.18</v>
@@ -5087,7 +5087,7 @@
         <v>1.47</v>
       </c>
       <c r="AE29">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AF29">
         <v>1.82</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O31">
         <v>3.4</v>
@@ -5371,25 +5371,25 @@
         <v>2.07</v>
       </c>
       <c r="Q31">
-        <v>3.72</v>
+        <v>3.86</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="S31">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.03</v>
@@ -5398,7 +5398,7 @@
         <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="AA31">
         <v>1.69</v>
@@ -5413,10 +5413,10 @@
         <v>1.39</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
         <v>2.28</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>2.19</v>
+        <v>3.65</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3.65</v>
+        <v>1.81</v>
       </c>
       <c r="Q33">
-        <v>2.29</v>
+        <v>4.23</v>
       </c>
       <c r="R33">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="S33">
+        <v>1.33</v>
+      </c>
+      <c r="T33">
+        <v>2.99</v>
+      </c>
+      <c r="U33">
+        <v>2.55</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1.21</v>
+      </c>
+      <c r="Z33">
+        <v>3.71</v>
+      </c>
+      <c r="AA33">
+        <v>1.8</v>
+      </c>
+      <c r="AB33">
+        <v>1.96</v>
+      </c>
+      <c r="AC33">
+        <v>2.88</v>
+      </c>
+      <c r="AD33">
+        <v>1.32</v>
+      </c>
+      <c r="AE33">
+        <v>1.1</v>
+      </c>
+      <c r="AF33">
+        <v>1.61</v>
+      </c>
+      <c r="AG33">
+        <v>2.1</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.25</v>
       </c>
-      <c r="T33">
-        <v>3.36</v>
-      </c>
-      <c r="U33">
-        <v>2.25</v>
-      </c>
-      <c r="V33">
-        <v>1.57</v>
-      </c>
-      <c r="W33">
-        <v>1.15</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.11</v>
-      </c>
-      <c r="Z33">
-        <v>4.81</v>
-      </c>
-      <c r="AA33">
-        <v>1.57</v>
-      </c>
-      <c r="AB33">
-        <v>2.3</v>
-      </c>
-      <c r="AC33">
-        <v>2.33</v>
-      </c>
-      <c r="AD33">
-        <v>1.57</v>
-      </c>
-      <c r="AE33">
-        <v>1.17</v>
-      </c>
-      <c r="AF33">
-        <v>1.49</v>
-      </c>
-      <c r="AG33">
-        <v>2.4</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.24</v>
-      </c>
       <c r="AK33">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="O37">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="P37">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.56</v>
@@ -6367,13 +6367,13 @@
         <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
         <v>3.62</v>
@@ -6382,19 +6382,19 @@
         <v>1.76</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC37">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AG37">
         <v>1.57</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6672,58 +6672,58 @@
         <v>3.35</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q39">
+        <v>3.15</v>
+      </c>
+      <c r="R39">
+        <v>2.14</v>
+      </c>
+      <c r="S39">
+        <v>1.35</v>
+      </c>
+      <c r="T39">
         <v>3.3</v>
       </c>
-      <c r="R39">
-        <v>2.13</v>
-      </c>
-      <c r="S39">
-        <v>1.37</v>
-      </c>
-      <c r="T39">
-        <v>3.08</v>
-      </c>
       <c r="U39">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V39">
         <v>1.48</v>
       </c>
       <c r="W39">
+        <v>1.09</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
+        <v>1.2</v>
+      </c>
+      <c r="Z39">
+        <v>3.94</v>
+      </c>
+      <c r="AA39">
+        <v>1.72</v>
+      </c>
+      <c r="AB39">
+        <v>2.12</v>
+      </c>
+      <c r="AC39">
+        <v>2.8</v>
+      </c>
+      <c r="AD39">
+        <v>1.39</v>
+      </c>
+      <c r="AE39">
         <v>1.11</v>
       </c>
-      <c r="X39">
-        <v>1.05</v>
-      </c>
-      <c r="Y39">
-        <v>1.21</v>
-      </c>
-      <c r="Z39">
-        <v>3.9</v>
-      </c>
-      <c r="AA39">
-        <v>1.73</v>
-      </c>
-      <c r="AB39">
-        <v>2.05</v>
-      </c>
-      <c r="AC39">
-        <v>3.05</v>
-      </c>
-      <c r="AD39">
-        <v>1.38</v>
-      </c>
-      <c r="AE39">
-        <v>1.09</v>
-      </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>3.2</v>
       </c>
       <c r="Q40">
+        <v>2.35</v>
+      </c>
+      <c r="R40">
+        <v>2.36</v>
+      </c>
+      <c r="S40">
+        <v>1.28</v>
+      </c>
+      <c r="T40">
+        <v>3.2</v>
+      </c>
+      <c r="U40">
+        <v>2.34</v>
+      </c>
+      <c r="V40">
+        <v>1.62</v>
+      </c>
+      <c r="W40">
+        <v>1.14</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.14</v>
+      </c>
+      <c r="Z40">
+        <v>4.7</v>
+      </c>
+      <c r="AA40">
+        <v>1.57</v>
+      </c>
+      <c r="AB40">
+        <v>2.37</v>
+      </c>
+      <c r="AC40">
         <v>2.55</v>
       </c>
-      <c r="R40">
-        <v>2.38</v>
-      </c>
-      <c r="S40">
-        <v>1.29</v>
-      </c>
-      <c r="T40">
-        <v>3.05</v>
-      </c>
-      <c r="U40">
-        <v>2.4</v>
-      </c>
-      <c r="V40">
-        <v>1.52</v>
-      </c>
-      <c r="W40">
-        <v>1.12</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.15</v>
-      </c>
-      <c r="Z40">
-        <v>4.8</v>
-      </c>
-      <c r="AA40">
-        <v>1.56</v>
-      </c>
-      <c r="AB40">
-        <v>2.23</v>
-      </c>
-      <c r="AC40">
-        <v>2.65</v>
-      </c>
       <c r="AD40">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF40">
         <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="O41">
-        <v>11</v>
+        <v>6.52</v>
       </c>
       <c r="P41">
-        <v>12</v>
+        <v>23.56</v>
       </c>
       <c r="Q41">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="R41">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="S41">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="U41">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="V41">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="W41">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z41">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AB41">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AC41">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="AD41">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AE41">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AG41">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="O42">
-        <v>6.52</v>
+        <v>11</v>
       </c>
       <c r="P42">
-        <v>23.56</v>
+        <v>13</v>
       </c>
       <c r="Q42">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="R42">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="S42">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="T42">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="U42">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="V42">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="W42">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
         <v>1.01</v>
       </c>
-      <c r="Y42">
-        <v>1.03</v>
-      </c>
       <c r="Z42">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA42">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AB42">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AC42">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AD42">
-        <v>2.21</v>
+        <v>3.05</v>
       </c>
       <c r="AE42">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK42">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q45">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S45">
         <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W45">
         <v>1.05</v>
@@ -7680,25 +7680,25 @@
         <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AB45">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC45">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD45">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE45">
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>1.72</v>
       </c>
       <c r="Q46">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="R46">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
         <v>1.38</v>
@@ -7828,43 +7828,43 @@
         <v>2.96</v>
       </c>
       <c r="U46">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
         <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y46">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA46">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB46">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC46">
         <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG46">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
         <v>2.69</v>
       </c>
       <c r="R47">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="T47">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="U47">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V47">
         <v>1.25</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y47">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z47">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB47">
         <v>1.53</v>
       </c>
       <c r="AC47">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD47">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AG47">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK47">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
         <v>4</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R48">
         <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T48">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="U48">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="V48">
         <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z48">
+        <v>3.1</v>
+      </c>
+      <c r="AA48">
+        <v>2.1</v>
+      </c>
+      <c r="AB48">
+        <v>1.83</v>
+      </c>
+      <c r="AC48">
         <v>3.5</v>
       </c>
-      <c r="AA48">
-        <v>2.08</v>
-      </c>
-      <c r="AB48">
-        <v>1.71</v>
-      </c>
-      <c r="AC48">
-        <v>3.3</v>
-      </c>
       <c r="AD48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
         <v>1.79</v>
       </c>
       <c r="AG48">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8468,37 +8468,37 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R50">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V50">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA50">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AB50">
         <v>2.5</v>
@@ -8507,16 +8507,16 @@
         <v>2.23</v>
       </c>
       <c r="AD50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF50">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AG50">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK50">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
+        <v>2.78</v>
+      </c>
+      <c r="O26">
+        <v>3.58</v>
+      </c>
+      <c r="P26">
+        <v>2.15</v>
+      </c>
+      <c r="Q26">
+        <v>3.74</v>
+      </c>
+      <c r="R26">
+        <v>2.21</v>
+      </c>
+      <c r="S26">
+        <v>1.35</v>
+      </c>
+      <c r="T26">
+        <v>3.18</v>
+      </c>
+      <c r="U26">
+        <v>2.76</v>
+      </c>
+      <c r="V26">
         <v>1.42</v>
       </c>
-      <c r="O26">
-        <v>4.8</v>
-      </c>
-      <c r="P26">
-        <v>5.8</v>
-      </c>
-      <c r="Q26">
-        <v>1.85</v>
-      </c>
-      <c r="R26">
-        <v>2.66</v>
-      </c>
-      <c r="S26">
-        <v>1.23</v>
-      </c>
-      <c r="T26">
-        <v>3.8</v>
-      </c>
-      <c r="U26">
-        <v>2.23</v>
-      </c>
-      <c r="V26">
-        <v>1.67</v>
-      </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
+        <v>1.21</v>
+      </c>
+      <c r="Z26">
+        <v>3.9</v>
+      </c>
+      <c r="AA26">
+        <v>1.8</v>
+      </c>
+      <c r="AB26">
+        <v>2</v>
+      </c>
+      <c r="AC26">
+        <v>3.15</v>
+      </c>
+      <c r="AD26">
+        <v>1.36</v>
+      </c>
+      <c r="AE26">
         <v>1.1</v>
       </c>
-      <c r="Z26">
-        <v>6</v>
-      </c>
-      <c r="AA26">
-        <v>1.44</v>
-      </c>
-      <c r="AB26">
-        <v>2.75</v>
-      </c>
-      <c r="AC26">
-        <v>2.18</v>
-      </c>
-      <c r="AD26">
-        <v>1.76</v>
-      </c>
-      <c r="AE26">
+      <c r="AF26">
+        <v>1.6</v>
+      </c>
+      <c r="AG26">
+        <v>2.17</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.25</v>
       </c>
-      <c r="AF26">
-        <v>1.65</v>
-      </c>
-      <c r="AG26">
-        <v>2.2</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.12</v>
-      </c>
       <c r="AK26">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.78</v>
+        <v>1.42</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>5.8</v>
       </c>
       <c r="Q27">
-        <v>3.74</v>
+        <v>1.85</v>
       </c>
       <c r="R27">
-        <v>2.21</v>
+        <v>2.66</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.76</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC27">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,10 +1130,10 @@
         <v>4.75</v>
       </c>
       <c r="P5">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="Q5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
         <v>2.71</v>
@@ -1148,40 +1148,40 @@
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB5">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q8">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
         <v>2.27</v>
@@ -1655,13 +1655,13 @@
         <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
         <v>2.38</v>
       </c>
       <c r="AD8">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE8">
         <v>1.21</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK8">
         <v>1.49</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-10 12:30:00</t>
+          <t>2026-09-10 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-10 13:00:00</t>
+          <t>2026-09-10 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fanja</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fanja</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G23">
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-10 13:15:00</t>
+          <t>2026-09-10 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>10</v>
+        <v>1.63</v>
       </c>
       <c r="O25">
-        <v>6.75</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>1.16</v>
+        <v>4.15</v>
       </c>
       <c r="Q25">
-        <v>8.289999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="R25">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
+        <v>1.21</v>
+      </c>
+      <c r="T25">
+        <v>3.3</v>
+      </c>
+      <c r="U25">
+        <v>2.13</v>
+      </c>
+      <c r="V25">
+        <v>1.61</v>
+      </c>
+      <c r="W25">
         <v>1.15</v>
       </c>
-      <c r="T25">
-        <v>4.75</v>
-      </c>
-      <c r="U25">
-        <v>1.86</v>
-      </c>
-      <c r="V25">
-        <v>1.87</v>
-      </c>
-      <c r="W25">
-        <v>1.22</v>
-      </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>6.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AB25">
-        <v>3.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG25">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>3.58</v>
+        <v>6.75</v>
       </c>
       <c r="P26">
-        <v>2.15</v>
+        <v>1.16</v>
       </c>
       <c r="Q26">
-        <v>3.74</v>
+        <v>7.7</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.99</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="U26">
-        <v>2.76</v>
+        <v>1.85</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AB26">
+        <v>3.25</v>
+      </c>
+      <c r="AC26">
+        <v>1.78</v>
+      </c>
+      <c r="AD26">
+        <v>1.92</v>
+      </c>
+      <c r="AE26">
+        <v>1.37</v>
+      </c>
+      <c r="AF26">
+        <v>1.69</v>
+      </c>
+      <c r="AG26">
         <v>2</v>
       </c>
-      <c r="AC26">
-        <v>3.15</v>
-      </c>
-      <c r="AD26">
-        <v>1.36</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
-      <c r="AF26">
-        <v>1.6</v>
-      </c>
-      <c r="AG26">
-        <v>2.17</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-10 13:45:00</t>
+          <t>2026-09-10 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,61 +4710,61 @@
         </is>
       </c>
       <c r="N27">
+        <v>3.2</v>
+      </c>
+      <c r="O27">
+        <v>3.5</v>
+      </c>
+      <c r="P27">
+        <v>2.15</v>
+      </c>
+      <c r="Q27">
+        <v>3.86</v>
+      </c>
+      <c r="R27">
+        <v>2.17</v>
+      </c>
+      <c r="S27">
+        <v>1.38</v>
+      </c>
+      <c r="T27">
+        <v>3.16</v>
+      </c>
+      <c r="U27">
+        <v>2.47</v>
+      </c>
+      <c r="V27">
         <v>1.42</v>
       </c>
-      <c r="O27">
-        <v>4.8</v>
-      </c>
-      <c r="P27">
-        <v>5.8</v>
-      </c>
-      <c r="Q27">
-        <v>1.85</v>
-      </c>
-      <c r="R27">
-        <v>2.66</v>
-      </c>
-      <c r="S27">
-        <v>1.23</v>
-      </c>
-      <c r="T27">
-        <v>3.8</v>
-      </c>
-      <c r="U27">
-        <v>2.23</v>
-      </c>
-      <c r="V27">
-        <v>1.67</v>
-      </c>
       <c r="W27">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AA27">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>2.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC27">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="AD27">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG27">
         <v>2.2</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>7.53</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>7.53</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>5.05</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="T30">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="U30">
-        <v>2.59</v>
+        <v>1.97</v>
       </c>
       <c r="V30">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z30">
-        <v>4.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC30">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK30">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.97</v>
+        <v>1.73</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.07</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>3.86</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AB31">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.65</v>
+        <v>2.07</v>
       </c>
       <c r="Q32">
-        <v>2.25</v>
+        <v>3.86</v>
       </c>
       <c r="R32">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z32">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA32">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AB32">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="AC32">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AD32">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="O33">
         <v>3.75</v>
       </c>
       <c r="P33">
-        <v>1.81</v>
+        <v>3.65</v>
       </c>
       <c r="Q33">
-        <v>4.23</v>
+        <v>2.25</v>
       </c>
       <c r="R33">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>3.71</v>
+        <v>5.8</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AB33">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00:00</t>
+          <t>2026-09-10 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="P38">
-        <v>4.05</v>
+        <v>9.5</v>
       </c>
       <c r="Q38">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V38">
+        <v>1.44</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.21</v>
+      </c>
+      <c r="Z38">
+        <v>3.62</v>
+      </c>
+      <c r="AA38">
+        <v>1.76</v>
+      </c>
+      <c r="AB38">
+        <v>2.05</v>
+      </c>
+      <c r="AC38">
+        <v>3.25</v>
+      </c>
+      <c r="AD38">
         <v>1.36</v>
       </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.28</v>
-      </c>
-      <c r="Z38">
-        <v>3.05</v>
-      </c>
-      <c r="AA38">
-        <v>2.04</v>
-      </c>
-      <c r="AB38">
-        <v>1.75</v>
-      </c>
-      <c r="AC38">
-        <v>3.42</v>
-      </c>
-      <c r="AD38">
-        <v>1.23</v>
-      </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-10 15:45:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="O39">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.68</v>
+        <v>4.05</v>
       </c>
       <c r="Q39">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="R39">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="U39">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB39">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="O40">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q40">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="R40">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="V40">
+        <v>1.49</v>
+      </c>
+      <c r="W40">
+        <v>1.09</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.2</v>
+      </c>
+      <c r="Z40">
+        <v>3.94</v>
+      </c>
+      <c r="AA40">
+        <v>1.78</v>
+      </c>
+      <c r="AB40">
+        <v>2.11</v>
+      </c>
+      <c r="AC40">
+        <v>2.97</v>
+      </c>
+      <c r="AD40">
+        <v>1.37</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
         <v>1.62</v>
       </c>
-      <c r="W40">
-        <v>1.14</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
-      <c r="Z40">
-        <v>4.7</v>
-      </c>
-      <c r="AA40">
-        <v>1.57</v>
-      </c>
-      <c r="AB40">
-        <v>2.37</v>
-      </c>
-      <c r="AC40">
-        <v>2.55</v>
-      </c>
-      <c r="AD40">
-        <v>1.59</v>
-      </c>
-      <c r="AE40">
-        <v>1.19</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
       <c r="AG40">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK40">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O41">
-        <v>6.52</v>
+        <v>11</v>
       </c>
       <c r="P41">
-        <v>23.56</v>
+        <v>13</v>
       </c>
       <c r="Q41">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="R41">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="T41">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="U41">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="V41">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="W41">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
         <v>1.01</v>
       </c>
-      <c r="Y41">
+      <c r="Z41">
+        <v>12</v>
+      </c>
+      <c r="AA41">
+        <v>1.1</v>
+      </c>
+      <c r="AB41">
+        <v>5.35</v>
+      </c>
+      <c r="AC41">
+        <v>1.37</v>
+      </c>
+      <c r="AD41">
+        <v>2.78</v>
+      </c>
+      <c r="AE41">
+        <v>1.87</v>
+      </c>
+      <c r="AF41">
+        <v>1.62</v>
+      </c>
+      <c r="AG41">
+        <v>2.2</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.03</v>
       </c>
-      <c r="Z41">
-        <v>7.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.24</v>
-      </c>
-      <c r="AB41">
-        <v>4</v>
-      </c>
-      <c r="AC41">
-        <v>1.69</v>
-      </c>
-      <c r="AD41">
-        <v>2.3</v>
-      </c>
-      <c r="AE41">
-        <v>1.53</v>
-      </c>
-      <c r="AF41">
-        <v>1.89</v>
-      </c>
-      <c r="AG41">
-        <v>1.78</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.09</v>
-      </c>
       <c r="AK41">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O42">
-        <v>11</v>
+        <v>6.52</v>
       </c>
       <c r="P42">
-        <v>13</v>
+        <v>23.56</v>
       </c>
       <c r="Q42">
         <v>1.33</v>
       </c>
       <c r="R42">
-        <v>4.2</v>
+        <v>3.06</v>
       </c>
       <c r="S42">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="T42">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="U42">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="V42">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="W42">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z42">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AC42">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD42">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE42">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.02</v>
       </c>
       <c r="AK42">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P46">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="Q46">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="R46">
         <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="U46">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V46">
         <v>1.38</v>
       </c>
       <c r="W46">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
         <v>1.9</v>
       </c>
       <c r="AB46">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD46">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AK46">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-10 16:15:00</t>
+          <t>2026-09-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,81 +7970,81 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q47">
-        <v>2.69</v>
+        <v>5</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="U47">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="V47">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W47">
+        <v>1.08</v>
+      </c>
+      <c r="X47">
         <v>1.01</v>
       </c>
-      <c r="X47">
-        <v>1.1</v>
-      </c>
       <c r="Y47">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="Z47">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="AA47">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="AB47">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC47">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
+        <v>1.27</v>
+      </c>
+      <c r="AE47">
+        <v>1.05</v>
+      </c>
+      <c r="AF47">
+        <v>1.85</v>
+      </c>
+      <c r="AG47">
+        <v>1.83</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.29</v>
+      </c>
+      <c r="AK47">
         <v>1.14</v>
       </c>
-      <c r="AE47">
-        <v>1.01</v>
-      </c>
-      <c r="AF47">
-        <v>1.88</v>
-      </c>
-      <c r="AG47">
-        <v>1.8</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.34</v>
-      </c>
-      <c r="AK47">
-        <v>1.66</v>
-      </c>
       <c r="AL47">
         <v>0</v>
       </c>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T48">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="U48">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="V48">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z48">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA48">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB48">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AC48">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD48">
+        <v>1.14</v>
+      </c>
+      <c r="AE48">
+        <v>1.01</v>
+      </c>
+      <c r="AF48">
+        <v>1.91</v>
+      </c>
+      <c r="AG48">
+        <v>1.65</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.25</v>
       </c>
-      <c r="AE48">
-        <v>1.05</v>
-      </c>
-      <c r="AF48">
-        <v>1.79</v>
-      </c>
-      <c r="AG48">
-        <v>1.77</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.28</v>
-      </c>
       <c r="AK48">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q49">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U49">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z49">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA49">
+        <v>2.1</v>
+      </c>
+      <c r="AB49">
         <v>1.73</v>
       </c>
-      <c r="AB49">
-        <v>1.91</v>
-      </c>
       <c r="AC49">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AD49">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-10 20:00:00</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8412,156 +8412,319 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>2.01</v>
+      </c>
+      <c r="O50">
+        <v>3.45</v>
+      </c>
+      <c r="P50">
+        <v>3.5</v>
+      </c>
+      <c r="Q50">
+        <v>2.45</v>
+      </c>
+      <c r="R50">
+        <v>2.28</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>2.43</v>
+      </c>
+      <c r="V50">
+        <v>1.42</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.55</v>
+      </c>
+      <c r="AA50">
+        <v>1.73</v>
+      </c>
+      <c r="AB50">
+        <v>1.91</v>
+      </c>
+      <c r="AC50">
+        <v>2.8</v>
+      </c>
+      <c r="AD50">
+        <v>1.34</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>1.63</v>
+      </c>
+      <c r="AG50">
+        <v>2.1</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.22</v>
+      </c>
+      <c r="AK50">
+        <v>1.65</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>1.44</v>
-      </c>
-      <c r="R50">
-        <v>3.1</v>
-      </c>
-      <c r="S50">
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>1.48</v>
+      </c>
+      <c r="R51">
+        <v>2.83</v>
+      </c>
+      <c r="S51">
         <v>1.22</v>
       </c>
-      <c r="T50">
-        <v>3.6</v>
-      </c>
-      <c r="U50">
-        <v>2.16</v>
-      </c>
-      <c r="V50">
+      <c r="T51">
+        <v>3.58</v>
+      </c>
+      <c r="U51">
+        <v>2.11</v>
+      </c>
+      <c r="V51">
         <v>1.63</v>
       </c>
-      <c r="W50">
+      <c r="W51">
+        <v>1.13</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
         <v>1.14</v>
       </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.12</v>
-      </c>
-      <c r="Z50">
-        <v>5.75</v>
-      </c>
-      <c r="AA50">
-        <v>1.42</v>
-      </c>
-      <c r="AB50">
+      <c r="Z51">
+        <v>5.38</v>
+      </c>
+      <c r="AA51">
+        <v>1.43</v>
+      </c>
+      <c r="AB51">
         <v>2.5</v>
       </c>
-      <c r="AC50">
+      <c r="AC51">
         <v>2.23</v>
       </c>
-      <c r="AD50">
-        <v>1.6</v>
-      </c>
-      <c r="AE50">
+      <c r="AD51">
+        <v>1.61</v>
+      </c>
+      <c r="AE51">
         <v>1.26</v>
       </c>
-      <c r="AF50">
-        <v>2.35</v>
-      </c>
-      <c r="AG50">
-        <v>1.53</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.07</v>
-      </c>
-      <c r="AK50">
+      <c r="AF51">
+        <v>2.2</v>
+      </c>
+      <c r="AG51">
+        <v>1.55</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.08</v>
+      </c>
+      <c r="AK51">
         <v>5</v>
       </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>2026-09-10 21:30:00</t>
         </is>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -4073,16 +4073,16 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.1</v>
@@ -4097,13 +4097,13 @@
         <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD23">
         <v>1.3</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AK23">
         <v>1.44</v>
@@ -5217,25 +5217,25 @@
         <v>1.19</v>
       </c>
       <c r="T30">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
         <v>1.97</v>
       </c>
       <c r="V30">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z30">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="AA30">
         <v>1.44</v>
@@ -5244,19 +5244,19 @@
         <v>2.62</v>
       </c>
       <c r="AC30">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AD30">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AE30">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="O31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U31">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA31">
         <v>1.77</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="AD31">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="R32">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
         <v>1.16</v>
       </c>
       <c r="Z32">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AE32">
         <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG32">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AK32">
         <v>1.31</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
+        <v>3.5</v>
+      </c>
+      <c r="O33">
+        <v>3.65</v>
+      </c>
+      <c r="P33">
+        <v>1.88</v>
+      </c>
+      <c r="Q33">
+        <v>3.8</v>
+      </c>
+      <c r="R33">
+        <v>2.3</v>
+      </c>
+      <c r="S33">
+        <v>1.33</v>
+      </c>
+      <c r="T33">
+        <v>2.99</v>
+      </c>
+      <c r="U33">
+        <v>2.68</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.06</v>
+      </c>
+      <c r="X33">
+        <v>1.05</v>
+      </c>
+      <c r="Y33">
+        <v>1.25</v>
+      </c>
+      <c r="Z33">
+        <v>3.7</v>
+      </c>
+      <c r="AA33">
         <v>1.8</v>
       </c>
-      <c r="O33">
-        <v>3.75</v>
-      </c>
-      <c r="P33">
-        <v>3.65</v>
-      </c>
-      <c r="Q33">
-        <v>2.25</v>
-      </c>
-      <c r="R33">
-        <v>2.63</v>
-      </c>
-      <c r="S33">
-        <v>1.25</v>
-      </c>
-      <c r="T33">
-        <v>3.36</v>
-      </c>
-      <c r="U33">
-        <v>2.29</v>
-      </c>
-      <c r="V33">
-        <v>1.57</v>
-      </c>
-      <c r="W33">
-        <v>1.1</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.1</v>
-      </c>
-      <c r="Z33">
-        <v>5.8</v>
-      </c>
-      <c r="AA33">
-        <v>1.38</v>
-      </c>
       <c r="AB33">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AC33">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="AD33">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.88</v>
+        <v>1.26</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
+        <v>1.8</v>
+      </c>
+      <c r="O34">
         <v>3.7</v>
       </c>
-      <c r="O34">
-        <v>3.75</v>
-      </c>
       <c r="P34">
-        <v>1.81</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>4.23</v>
+        <v>2.25</v>
       </c>
       <c r="R34">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="U34">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>3.71</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="AD34">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="P39">
-        <v>4.05</v>
+        <v>9.5</v>
       </c>
       <c r="Q39">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="AA39">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AG39">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-10 15:45:00</t>
+          <t>2026-09-10 15:15:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.54</v>
+        <v>1.81</v>
       </c>
       <c r="O40">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="Q40">
-        <v>3.14</v>
+        <v>2.46</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
+        <v>2.79</v>
+      </c>
+      <c r="U40">
+        <v>2.8</v>
+      </c>
+      <c r="V40">
+        <v>1.36</v>
+      </c>
+      <c r="W40">
+        <v>1.07</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.3</v>
+      </c>
+      <c r="Z40">
         <v>3.05</v>
       </c>
-      <c r="U40">
-        <v>2.6</v>
-      </c>
-      <c r="V40">
-        <v>1.49</v>
-      </c>
-      <c r="W40">
-        <v>1.09</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.2</v>
-      </c>
-      <c r="Z40">
-        <v>3.94</v>
-      </c>
       <c r="AA40">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="AB40">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AC40">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG40">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.12</v>
+        <v>2.54</v>
       </c>
       <c r="O41">
-        <v>11</v>
+        <v>3.44</v>
       </c>
       <c r="P41">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="Q41">
+        <v>3.14</v>
+      </c>
+      <c r="R41">
+        <v>2.2</v>
+      </c>
+      <c r="S41">
         <v>1.32</v>
       </c>
-      <c r="R41">
-        <v>4.3</v>
-      </c>
-      <c r="S41">
-        <v>1.08</v>
-      </c>
       <c r="T41">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="U41">
-        <v>1.51</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="W41">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>12</v>
+        <v>3.94</v>
       </c>
       <c r="AA41">
+        <v>1.78</v>
+      </c>
+      <c r="AB41">
+        <v>2.11</v>
+      </c>
+      <c r="AC41">
+        <v>2.97</v>
+      </c>
+      <c r="AD41">
+        <v>1.37</v>
+      </c>
+      <c r="AE41">
         <v>1.1</v>
-      </c>
-      <c r="AB41">
-        <v>5.35</v>
-      </c>
-      <c r="AC41">
-        <v>1.37</v>
-      </c>
-      <c r="AD41">
-        <v>2.78</v>
-      </c>
-      <c r="AE41">
-        <v>1.87</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AK41">
-        <v>7</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O42">
-        <v>6.52</v>
+        <v>11</v>
       </c>
       <c r="P42">
-        <v>23.56</v>
+        <v>13</v>
       </c>
       <c r="Q42">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R42">
-        <v>3.06</v>
+        <v>4.3</v>
       </c>
       <c r="S42">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="T42">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="U42">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="V42">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="W42">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
         <v>1.01</v>
       </c>
-      <c r="Y42">
-        <v>1.04</v>
-      </c>
       <c r="Z42">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA42">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AB42">
-        <v>4</v>
+        <v>5.35</v>
       </c>
       <c r="AC42">
+        <v>1.37</v>
+      </c>
+      <c r="AD42">
+        <v>2.78</v>
+      </c>
+      <c r="AE42">
+        <v>1.87</v>
+      </c>
+      <c r="AF42">
         <v>1.62</v>
       </c>
-      <c r="AD42">
+      <c r="AG42">
         <v>2.2</v>
       </c>
-      <c r="AE42">
-        <v>1.53</v>
-      </c>
-      <c r="AF42">
-        <v>1.92</v>
-      </c>
-      <c r="AG42">
-        <v>1.8</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK42">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="O43">
-        <v>3.95</v>
+        <v>6.52</v>
       </c>
       <c r="P43">
-        <v>3.95</v>
+        <v>23.56</v>
       </c>
       <c r="Q43">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R43">
-        <v>2.27</v>
+        <v>3.06</v>
       </c>
       <c r="S43">
+        <v>1.13</v>
+      </c>
+      <c r="T43">
+        <v>5.4</v>
+      </c>
+      <c r="U43">
+        <v>1.86</v>
+      </c>
+      <c r="V43">
+        <v>2.09</v>
+      </c>
+      <c r="W43">
         <v>1.29</v>
-      </c>
-      <c r="T43">
-        <v>3.2</v>
-      </c>
-      <c r="U43">
-        <v>2.32</v>
-      </c>
-      <c r="V43">
-        <v>1.63</v>
-      </c>
-      <c r="W43">
-        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA43">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AB43">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="AC43">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD43">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AE43">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>1.91</v>
+        <v>6.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="O46">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="Q46">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="U46">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V46">
         <v>1.38</v>
       </c>
       <c r="W46">
+        <v>1.08</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.27</v>
+      </c>
+      <c r="Z46">
+        <v>3.35</v>
+      </c>
+      <c r="AA46">
+        <v>2.01</v>
+      </c>
+      <c r="AB46">
+        <v>1.83</v>
+      </c>
+      <c r="AC46">
+        <v>3.3</v>
+      </c>
+      <c r="AD46">
+        <v>1.27</v>
+      </c>
+      <c r="AE46">
         <v>1.05</v>
       </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.3</v>
-      </c>
-      <c r="Z46">
-        <v>3.5</v>
-      </c>
-      <c r="AA46">
-        <v>1.9</v>
-      </c>
-      <c r="AB46">
-        <v>1.8</v>
-      </c>
-      <c r="AC46">
-        <v>3.24</v>
-      </c>
-      <c r="AD46">
-        <v>1.3</v>
-      </c>
-      <c r="AE46">
-        <v>1.06</v>
-      </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG46">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-10 16:00:00</t>
+          <t>2026-09-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-10 16:15:00</t>
+          <t>2026-09-10 17:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.12</v>
+        <v>1.88</v>
       </c>
       <c r="O42">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="P42">
-        <v>13</v>
+        <v>3.95</v>
       </c>
       <c r="Q42">
-        <v>1.32</v>
+        <v>2.33</v>
       </c>
       <c r="R42">
-        <v>4.3</v>
+        <v>2.27</v>
       </c>
       <c r="S42">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="V42">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="W42">
+        <v>1.14</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
+        <v>1.14</v>
+      </c>
+      <c r="Z42">
+        <v>5</v>
+      </c>
+      <c r="AA42">
+        <v>1.61</v>
+      </c>
+      <c r="AB42">
+        <v>2.27</v>
+      </c>
+      <c r="AC42">
+        <v>2.55</v>
+      </c>
+      <c r="AD42">
+        <v>1.52</v>
+      </c>
+      <c r="AE42">
+        <v>1.19</v>
+      </c>
+      <c r="AF42">
         <v>1.5</v>
       </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>1.01</v>
-      </c>
-      <c r="Z42">
-        <v>12</v>
-      </c>
-      <c r="AA42">
-        <v>1.1</v>
-      </c>
-      <c r="AB42">
-        <v>5.35</v>
-      </c>
-      <c r="AC42">
-        <v>1.37</v>
-      </c>
-      <c r="AD42">
-        <v>2.78</v>
-      </c>
-      <c r="AE42">
-        <v>1.87</v>
-      </c>
-      <c r="AF42">
-        <v>1.62</v>
-      </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O43">
-        <v>6.52</v>
+        <v>11</v>
       </c>
       <c r="P43">
-        <v>23.56</v>
+        <v>13</v>
       </c>
       <c r="Q43">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R43">
-        <v>3.06</v>
+        <v>4.3</v>
       </c>
       <c r="S43">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="T43">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="U43">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="V43">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="W43">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.01</v>
       </c>
-      <c r="Y43">
-        <v>1.04</v>
-      </c>
       <c r="Z43">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA43">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AB43">
-        <v>4</v>
+        <v>5.35</v>
       </c>
       <c r="AC43">
+        <v>1.37</v>
+      </c>
+      <c r="AD43">
+        <v>2.78</v>
+      </c>
+      <c r="AE43">
+        <v>1.87</v>
+      </c>
+      <c r="AF43">
         <v>1.62</v>
       </c>
-      <c r="AD43">
+      <c r="AG43">
         <v>2.2</v>
       </c>
-      <c r="AE43">
-        <v>1.53</v>
-      </c>
-      <c r="AF43">
-        <v>1.92</v>
-      </c>
-      <c r="AG43">
-        <v>1.8</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK43">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="O44">
-        <v>3.95</v>
+        <v>6.52</v>
       </c>
       <c r="P44">
-        <v>3.95</v>
+        <v>23.56</v>
       </c>
       <c r="Q44">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="R44">
-        <v>2.27</v>
+        <v>3.06</v>
       </c>
       <c r="S44">
+        <v>1.13</v>
+      </c>
+      <c r="T44">
+        <v>5.4</v>
+      </c>
+      <c r="U44">
+        <v>1.86</v>
+      </c>
+      <c r="V44">
+        <v>2.09</v>
+      </c>
+      <c r="W44">
         <v>1.29</v>
-      </c>
-      <c r="T44">
-        <v>3.2</v>
-      </c>
-      <c r="U44">
-        <v>2.32</v>
-      </c>
-      <c r="V44">
-        <v>1.63</v>
-      </c>
-      <c r="W44">
-        <v>1.14</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z44">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AB44">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD44">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AE44">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>6.25</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="O39">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="P39">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R39">
         <v>2.45</v>
@@ -6687,16 +6687,16 @@
         <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.21</v>
@@ -6705,22 +6705,22 @@
         <v>3.62</v>
       </c>
       <c r="AA39">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC39">
         <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG39">
         <v>1.57</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
         <v>3.6</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.88</v>
+        <v>1.12</v>
       </c>
       <c r="O42">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="P42">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="Q42">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="R42">
-        <v>2.27</v>
+        <v>4.3</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="V42">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
         <v>1.01</v>
       </c>
-      <c r="Y42">
-        <v>1.14</v>
-      </c>
       <c r="Z42">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AA42">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="AB42">
-        <v>2.27</v>
+        <v>5.35</v>
       </c>
       <c r="AC42">
-        <v>2.55</v>
+        <v>1.37</v>
       </c>
       <c r="AD42">
-        <v>1.52</v>
+        <v>2.78</v>
       </c>
       <c r="AE42">
-        <v>1.19</v>
+        <v>1.87</v>
       </c>
       <c r="AF42">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AK42">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>6.52</v>
       </c>
       <c r="P43">
-        <v>13</v>
+        <v>23.56</v>
       </c>
       <c r="Q43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R43">
-        <v>4.3</v>
+        <v>3.06</v>
       </c>
       <c r="S43">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T43">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="U43">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="V43">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="W43">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z43">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AA43">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AB43">
-        <v>5.35</v>
+        <v>4</v>
       </c>
       <c r="AC43">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AD43">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="AE43">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AG43">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.88</v>
+      </c>
+      <c r="O44">
+        <v>3.95</v>
+      </c>
+      <c r="P44">
+        <v>3.95</v>
+      </c>
+      <c r="Q44">
+        <v>2.33</v>
+      </c>
+      <c r="R44">
+        <v>2.27</v>
+      </c>
+      <c r="S44">
+        <v>1.29</v>
+      </c>
+      <c r="T44">
+        <v>3.2</v>
+      </c>
+      <c r="U44">
+        <v>2.32</v>
+      </c>
+      <c r="V44">
+        <v>1.63</v>
+      </c>
+      <c r="W44">
         <v>1.14</v>
-      </c>
-      <c r="O44">
-        <v>6.52</v>
-      </c>
-      <c r="P44">
-        <v>23.56</v>
-      </c>
-      <c r="Q44">
-        <v>1.33</v>
-      </c>
-      <c r="R44">
-        <v>3.06</v>
-      </c>
-      <c r="S44">
-        <v>1.13</v>
-      </c>
-      <c r="T44">
-        <v>5.4</v>
-      </c>
-      <c r="U44">
-        <v>1.86</v>
-      </c>
-      <c r="V44">
-        <v>2.09</v>
-      </c>
-      <c r="W44">
-        <v>1.29</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="AC44">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AE44">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>6.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O5">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R5">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
         <v>1.17</v>
       </c>
       <c r="T5">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V5">
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA5">
         <v>1.48</v>
@@ -1172,10 +1172,10 @@
         <v>2.15</v>
       </c>
       <c r="AD5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
         <v>1.58</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="O8">
+        <v>3.48</v>
+      </c>
+      <c r="P8">
+        <v>2.05</v>
+      </c>
+      <c r="Q8">
+        <v>2.61</v>
+      </c>
+      <c r="R8">
+        <v>2.45</v>
+      </c>
+      <c r="S8">
+        <v>1.21</v>
+      </c>
+      <c r="T8">
         <v>3.6</v>
       </c>
-      <c r="P8">
-        <v>2.85</v>
-      </c>
-      <c r="Q8">
-        <v>2.75</v>
-      </c>
-      <c r="R8">
-        <v>2.27</v>
-      </c>
-      <c r="S8">
-        <v>1.24</v>
-      </c>
-      <c r="T8">
-        <v>3.48</v>
-      </c>
       <c r="U8">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
+        <v>1.13</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
         <v>1.12</v>
       </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
+      <c r="Z8">
+        <v>4.65</v>
+      </c>
+      <c r="AA8">
+        <v>1.53</v>
+      </c>
+      <c r="AB8">
+        <v>2.3</v>
+      </c>
+      <c r="AC8">
+        <v>2.28</v>
+      </c>
+      <c r="AD8">
+        <v>1.53</v>
+      </c>
+      <c r="AE8">
         <v>1.17</v>
       </c>
-      <c r="Z8">
-        <v>4.63</v>
-      </c>
-      <c r="AA8">
-        <v>1.57</v>
-      </c>
-      <c r="AB8">
-        <v>2.25</v>
-      </c>
-      <c r="AC8">
-        <v>2.38</v>
-      </c>
-      <c r="AD8">
-        <v>1.52</v>
-      </c>
-      <c r="AE8">
-        <v>1.21</v>
-      </c>
       <c r="AF8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
         <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
         <v>1.81</v>
@@ -4103,19 +4103,19 @@
         <v>1.88</v>
       </c>
       <c r="AC23">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O25">
         <v>4.1</v>
@@ -4393,13 +4393,13 @@
         <v>4.15</v>
       </c>
       <c r="Q25">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
         <v>3.3</v>
@@ -4417,10 +4417,10 @@
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
         <v>1.47</v>
@@ -4432,7 +4432,7 @@
         <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE25">
         <v>1.2</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="P26">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Q26">
         <v>7.7</v>
@@ -4568,13 +4568,13 @@
         <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V26">
         <v>1.87</v>
       </c>
       <c r="W26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,7 +4583,7 @@
         <v>1.05</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA26">
         <v>1.3</v>
@@ -4598,13 +4598,13 @@
         <v>1.92</v>
       </c>
       <c r="AE26">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AF26">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="AK26">
         <v>1.05</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
         <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q27">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4746,28 +4746,28 @@
         <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC27">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,61 +4876,61 @@
         <v>1.41</v>
       </c>
       <c r="O28">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="P28">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="Q28">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R28">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
         <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V28">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
         <v>1.19</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA28">
         <v>1.44</v>
       </c>
       <c r="AB28">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AC28">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD28">
         <v>1.69</v>
       </c>
       <c r="AE28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>1.3</v>
       </c>
       <c r="Q30">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="S30">
         <v>1.19</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="U30">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V30">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="AA30">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB30">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="AC30">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AD30">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="R31">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
         <v>1.33</v>
@@ -5383,43 +5383,43 @@
         <v>2.99</v>
       </c>
       <c r="U31">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA31">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="AD31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,25 +5534,25 @@
         <v>2</v>
       </c>
       <c r="Q32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,19 +5564,19 @@
         <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AD32">
         <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
         <v>1.56</v>
@@ -5598,7 +5598,7 @@
         <v>1.56</v>
       </c>
       <c r="AK32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="O33">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="P33">
         <v>1.88</v>
@@ -5709,7 +5709,7 @@
         <v>2.99</v>
       </c>
       <c r="U33">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
         <v>1.44</v>
@@ -5721,31 +5721,31 @@
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
         <v>2</v>
       </c>
       <c r="AC33">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>1.8</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q34">
         <v>2.25</v>
@@ -5884,7 +5884,7 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -5893,22 +5893,22 @@
         <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
         <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="O40">
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q40">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="R40">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
         <v>2.8</v>
@@ -6856,7 +6856,7 @@
         <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6865,16 +6865,16 @@
         <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AA40">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AB40">
         <v>1.73</v>
       </c>
       <c r="AC40">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AD40">
         <v>1.23</v>
@@ -6902,7 +6902,7 @@
         <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,55 +6992,55 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V41">
         <v>1.49</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AA41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AD41">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
         <v>1.1</v>
@@ -7049,7 +7049,7 @@
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AK41">
         <v>1.44</v>
@@ -7164,10 +7164,10 @@
         <v>13</v>
       </c>
       <c r="Q42">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="R42">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="S42">
         <v>1.08</v>
@@ -7176,43 +7176,43 @@
         <v>7.5</v>
       </c>
       <c r="U42">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="V42">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="W42">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB42">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AC42">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AD42">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AE42">
         <v>1.87</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK42">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,10 +7327,10 @@
         <v>23.56</v>
       </c>
       <c r="Q43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R43">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="S43">
         <v>1.13</v>
@@ -7339,22 +7339,22 @@
         <v>5.4</v>
       </c>
       <c r="U43">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V43">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="W43">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="AA43">
         <v>1.25</v>
@@ -7363,16 +7363,16 @@
         <v>4</v>
       </c>
       <c r="AC43">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AD43">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AE43">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AF43">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG43">
         <v>1.8</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AK43">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O44">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="R44">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V44">
         <v>1.63</v>
@@ -7517,22 +7517,22 @@
         <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AB44">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD44">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE44">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
         <v>1.5</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,16 +7644,16 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="O45">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="P45">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q45">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="R45">
         <v>2.1</v>
@@ -7662,31 +7662,31 @@
         <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB45">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
         <v>3.24</v>
@@ -7698,10 +7698,10 @@
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
         <v>1.35</v>
@@ -7813,58 +7813,58 @@
         <v>3.7</v>
       </c>
       <c r="P46">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q46">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U46">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V46">
         <v>1.38</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA46">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AB46">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD46">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG46">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q48">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="R48">
         <v>2</v>
@@ -8154,10 +8154,10 @@
         <v>2.32</v>
       </c>
       <c r="U48">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V48">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W48">
         <v>1.01</v>
@@ -8166,13 +8166,13 @@
         <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z48">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="AA48">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB48">
         <v>1.5</v>
@@ -8184,13 +8184,13 @@
         <v>1.14</v>
       </c>
       <c r="AE48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O49">
         <v>3.3</v>
@@ -8305,55 +8305,55 @@
         <v>4</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R49">
         <v>2.05</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T49">
         <v>2.53</v>
       </c>
       <c r="U49">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="V49">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
         <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC49">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8631,37 +8631,37 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R51">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="S51">
         <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V51">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z51">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="AA51">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB51">
         <v>2.5</v>
@@ -8670,16 +8670,16 @@
         <v>2.23</v>
       </c>
       <c r="AD51">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AE51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF51">
         <v>2.2</v>
       </c>
       <c r="AG51">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK51">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4719,25 +4719,25 @@
         <v>2.06</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R27">
         <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U27">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4746,19 +4746,19 @@
         <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA27">
         <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
         <v>2.68</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4909,7 +4909,7 @@
         <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>1.44</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5214,10 +5214,10 @@
         <v>2.95</v>
       </c>
       <c r="S30">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U30">
         <v>1.95</v>
@@ -5226,34 +5226,34 @@
         <v>1.77</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA30">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AB30">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="AC30">
         <v>2</v>
       </c>
       <c r="AD30">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
         <v>1.75</v>
@@ -5374,7 +5374,7 @@
         <v>2.19</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S31">
         <v>1.33</v>
@@ -5383,7 +5383,7 @@
         <v>2.99</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -5398,7 +5398,7 @@
         <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
         <v>1.8</v>
@@ -5407,7 +5407,7 @@
         <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
         <v>1.33</v>
@@ -5416,10 +5416,10 @@
         <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>3.9</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.3</v>
@@ -5546,13 +5546,13 @@
         <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5561,7 +5561,7 @@
         <v>1.16</v>
       </c>
       <c r="Z32">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA32">
         <v>1.66</v>
@@ -5573,7 +5573,7 @@
         <v>2.45</v>
       </c>
       <c r="AD32">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE32">
         <v>1.16</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AK32">
         <v>1.3</v>
@@ -5694,13 +5694,13 @@
         <v>3.21</v>
       </c>
       <c r="P33">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q33">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
         <v>1.33</v>
@@ -5712,19 +5712,19 @@
         <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA33">
         <v>1.83</v>
@@ -5739,10 +5739,10 @@
         <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
         <v>2.1</v>
@@ -5884,25 +5884,25 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA34">
+        <v>1.52</v>
+      </c>
+      <c r="AB34">
+        <v>2.33</v>
+      </c>
+      <c r="AC34">
+        <v>2.4</v>
+      </c>
+      <c r="AD34">
         <v>1.57</v>
       </c>
-      <c r="AB34">
-        <v>2.4</v>
-      </c>
-      <c r="AC34">
-        <v>2.3</v>
-      </c>
-      <c r="AD34">
-        <v>1.53</v>
-      </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
         <v>1.5</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S41">
         <v>1.34</v>
@@ -7040,16 +7040,16 @@
         <v>2.8</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
         <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O42">
-        <v>11</v>
+        <v>6.52</v>
       </c>
       <c r="P42">
-        <v>13</v>
+        <v>23.56</v>
       </c>
       <c r="Q42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R42">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="S42">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T42">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="U42">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="V42">
-        <v>2.49</v>
+        <v>1.98</v>
       </c>
       <c r="W42">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z42">
-        <v>15</v>
+        <v>7.3</v>
       </c>
       <c r="AA42">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AB42">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AC42">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AD42">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="AE42">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AF42">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AG42">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.91</v>
+      </c>
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43">
+        <v>3.7</v>
+      </c>
+      <c r="Q43">
+        <v>2.35</v>
+      </c>
+      <c r="R43">
+        <v>2.38</v>
+      </c>
+      <c r="S43">
+        <v>1.28</v>
+      </c>
+      <c r="T43">
+        <v>3.4</v>
+      </c>
+      <c r="U43">
+        <v>2.19</v>
+      </c>
+      <c r="V43">
+        <v>1.63</v>
+      </c>
+      <c r="W43">
         <v>1.14</v>
-      </c>
-      <c r="O43">
-        <v>6.52</v>
-      </c>
-      <c r="P43">
-        <v>23.56</v>
-      </c>
-      <c r="Q43">
-        <v>1.36</v>
-      </c>
-      <c r="R43">
-        <v>3.6</v>
-      </c>
-      <c r="S43">
-        <v>1.13</v>
-      </c>
-      <c r="T43">
-        <v>5.4</v>
-      </c>
-      <c r="U43">
-        <v>1.76</v>
-      </c>
-      <c r="V43">
-        <v>1.98</v>
-      </c>
-      <c r="W43">
-        <v>1.31</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>7.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA43">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AB43">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="AC43">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD43">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P44">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="Q44">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="S44">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="U44">
-        <v>2.19</v>
+        <v>1.53</v>
       </c>
       <c r="V44">
+        <v>2.49</v>
+      </c>
+      <c r="W44">
+        <v>1.47</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.02</v>
+      </c>
+      <c r="Z44">
+        <v>15</v>
+      </c>
+      <c r="AA44">
+        <v>1.14</v>
+      </c>
+      <c r="AB44">
+        <v>5.75</v>
+      </c>
+      <c r="AC44">
+        <v>1.35</v>
+      </c>
+      <c r="AD44">
+        <v>2.9</v>
+      </c>
+      <c r="AE44">
+        <v>1.91</v>
+      </c>
+      <c r="AF44">
         <v>1.63</v>
       </c>
-      <c r="W44">
-        <v>1.14</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.14</v>
-      </c>
-      <c r="Z44">
-        <v>4.75</v>
-      </c>
-      <c r="AA44">
-        <v>1.54</v>
-      </c>
-      <c r="AB44">
-        <v>2.47</v>
-      </c>
-      <c r="AC44">
-        <v>2.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.53</v>
-      </c>
-      <c r="AE44">
-        <v>1.17</v>
-      </c>
-      <c r="AF44">
-        <v>1.5</v>
-      </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK44">
-        <v>1.85</v>
+        <v>7.5</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.12</v>
+      </c>
+      <c r="O43">
+        <v>11</v>
+      </c>
+      <c r="P43">
+        <v>13</v>
+      </c>
+      <c r="Q43">
+        <v>1.36</v>
+      </c>
+      <c r="R43">
+        <v>3.8</v>
+      </c>
+      <c r="S43">
+        <v>1.08</v>
+      </c>
+      <c r="T43">
+        <v>7.5</v>
+      </c>
+      <c r="U43">
+        <v>1.53</v>
+      </c>
+      <c r="V43">
+        <v>2.49</v>
+      </c>
+      <c r="W43">
+        <v>1.47</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.02</v>
+      </c>
+      <c r="Z43">
+        <v>15</v>
+      </c>
+      <c r="AA43">
+        <v>1.14</v>
+      </c>
+      <c r="AB43">
+        <v>5.75</v>
+      </c>
+      <c r="AC43">
+        <v>1.35</v>
+      </c>
+      <c r="AD43">
+        <v>2.9</v>
+      </c>
+      <c r="AE43">
         <v>1.91</v>
       </c>
-      <c r="O43">
-        <v>4</v>
-      </c>
-      <c r="P43">
-        <v>3.7</v>
-      </c>
-      <c r="Q43">
-        <v>2.35</v>
-      </c>
-      <c r="R43">
-        <v>2.38</v>
-      </c>
-      <c r="S43">
-        <v>1.28</v>
-      </c>
-      <c r="T43">
-        <v>3.4</v>
-      </c>
-      <c r="U43">
-        <v>2.19</v>
-      </c>
-      <c r="V43">
+      <c r="AF43">
         <v>1.63</v>
       </c>
-      <c r="W43">
-        <v>1.14</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>4.75</v>
-      </c>
-      <c r="AA43">
-        <v>1.54</v>
-      </c>
-      <c r="AB43">
-        <v>2.37</v>
-      </c>
-      <c r="AC43">
-        <v>2.4</v>
-      </c>
-      <c r="AD43">
-        <v>1.52</v>
-      </c>
-      <c r="AE43">
-        <v>1.18</v>
-      </c>
-      <c r="AF43">
-        <v>1.5</v>
-      </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK43">
-        <v>1.85</v>
+        <v>7.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="O44">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="R44">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="V44">
-        <v>2.49</v>
+        <v>1.63</v>
       </c>
       <c r="W44">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>15</v>
+        <v>4.75</v>
       </c>
       <c r="AA44">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="AB44">
-        <v>5.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC44">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD44">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="AE44">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O48">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
         <v>3.5</v>
@@ -8145,7 +8145,7 @@
         <v>2.67</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S48">
         <v>1.53</v>
@@ -8163,10 +8163,10 @@
         <v>1.01</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y48">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z48">
         <v>2.43</v>
@@ -8178,16 +8178,16 @@
         <v>1.5</v>
       </c>
       <c r="AC48">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD48">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE48">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG48">
         <v>1.66</v>
@@ -8326,13 +8326,13 @@
         <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y49">
         <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AA49">
         <v>2.04</v>
@@ -8350,7 +8350,7 @@
         <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG49">
         <v>1.78</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="S51">
         <v>1.22</v>
@@ -8643,7 +8643,7 @@
         <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V51">
         <v>1.65</v>
@@ -8658,16 +8658,16 @@
         <v>1.09</v>
       </c>
       <c r="Z51">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA51">
         <v>1.5</v>
       </c>
       <c r="AB51">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC51">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AD51">
         <v>1.67</v>
@@ -8676,7 +8676,7 @@
         <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AG51">
         <v>1.5</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK51">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O5">
         <v>4.8</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>4.71</v>
       </c>
       <c r="Q5">
         <v>1.85</v>
@@ -1139,10 +1139,10 @@
         <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U5">
         <v>2.07</v>
@@ -1154,22 +1154,22 @@
         <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC5">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
         <v>1.62</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1622,31 +1622,31 @@
         <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
         <v>3.6</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V8">
         <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z8">
         <v>4.65</v>
@@ -1655,16 +1655,16 @@
         <v>1.53</v>
       </c>
       <c r="AB8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC8">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AD8">
         <v>1.53</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
         <v>1.5</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>3.02</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4085,7 +4085,7 @@
         <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4097,10 +4097,10 @@
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB23">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
         <v>3.25</v>
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG23">
         <v>2.1</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
+        <v>1.24</v>
+      </c>
+      <c r="AK23">
         <v>1.4</v>
-      </c>
-      <c r="AK23">
-        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>1.48</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q25">
         <v>2.15</v>
@@ -4399,22 +4399,22 @@
         <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
         <v>2.13</v>
       </c>
       <c r="V25">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
@@ -4423,13 +4423,13 @@
         <v>4.75</v>
       </c>
       <c r="AA25">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD25">
         <v>1.53</v>
@@ -4438,10 +4438,10 @@
         <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O26">
         <v>6.6</v>
@@ -4556,22 +4556,22 @@
         <v>1.08</v>
       </c>
       <c r="Q26">
-        <v>7.7</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R26">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="S26">
         <v>1.17</v>
       </c>
       <c r="T26">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U26">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V26">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W26">
         <v>1.22</v>
@@ -4583,28 +4583,28 @@
         <v>1.05</v>
       </c>
       <c r="Z26">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>1.3</v>
       </c>
       <c r="AB26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AC26">
         <v>1.78</v>
       </c>
       <c r="AD26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G37">
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-09-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,22 +6666,22 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="O39">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P39">
-        <v>10.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q39">
         <v>1.73</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
         <v>3.25</v>
@@ -6693,37 +6693,37 @@
         <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA39">
         <v>1.75</v>
       </c>
       <c r="AB39">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AG39">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.13</v>
       </c>
       <c r="AK39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q40">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R40">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S40">
         <v>1.4</v>
@@ -6850,37 +6850,37 @@
         <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V40">
         <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="AA40">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC40">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AD40">
         <v>1.23</v>
       </c>
       <c r="AE40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
         <v>1.83</v>
@@ -6902,7 +6902,7 @@
         <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="Q43">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="R43">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="U43">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="V43">
-        <v>2.49</v>
+        <v>1.63</v>
       </c>
       <c r="W43">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>15</v>
+        <v>4.75</v>
       </c>
       <c r="AA43">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="AB43">
-        <v>5.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC43">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD43">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="AE43">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.12</v>
+      </c>
+      <c r="O44">
+        <v>11</v>
+      </c>
+      <c r="P44">
+        <v>13</v>
+      </c>
+      <c r="Q44">
+        <v>1.36</v>
+      </c>
+      <c r="R44">
+        <v>3.8</v>
+      </c>
+      <c r="S44">
+        <v>1.08</v>
+      </c>
+      <c r="T44">
+        <v>7.5</v>
+      </c>
+      <c r="U44">
+        <v>1.53</v>
+      </c>
+      <c r="V44">
+        <v>2.49</v>
+      </c>
+      <c r="W44">
+        <v>1.47</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.02</v>
+      </c>
+      <c r="Z44">
+        <v>15</v>
+      </c>
+      <c r="AA44">
+        <v>1.14</v>
+      </c>
+      <c r="AB44">
+        <v>5.75</v>
+      </c>
+      <c r="AC44">
+        <v>1.35</v>
+      </c>
+      <c r="AD44">
+        <v>2.9</v>
+      </c>
+      <c r="AE44">
         <v>1.91</v>
       </c>
-      <c r="O44">
-        <v>4</v>
-      </c>
-      <c r="P44">
-        <v>3.7</v>
-      </c>
-      <c r="Q44">
-        <v>2.35</v>
-      </c>
-      <c r="R44">
-        <v>2.38</v>
-      </c>
-      <c r="S44">
-        <v>1.28</v>
-      </c>
-      <c r="T44">
-        <v>3.4</v>
-      </c>
-      <c r="U44">
-        <v>2.19</v>
-      </c>
-      <c r="V44">
+      <c r="AF44">
         <v>1.63</v>
       </c>
-      <c r="W44">
-        <v>1.14</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.14</v>
-      </c>
-      <c r="Z44">
-        <v>4.75</v>
-      </c>
-      <c r="AA44">
-        <v>1.54</v>
-      </c>
-      <c r="AB44">
-        <v>2.37</v>
-      </c>
-      <c r="AC44">
-        <v>2.4</v>
-      </c>
-      <c r="AD44">
-        <v>1.52</v>
-      </c>
-      <c r="AE44">
-        <v>1.18</v>
-      </c>
-      <c r="AF44">
-        <v>1.5</v>
-      </c>
       <c r="AG44">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK44">
-        <v>1.85</v>
+        <v>7.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="O45">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q45">
-        <v>3.2</v>
+        <v>3.73</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S45">
         <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U45">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7680,10 +7680,10 @@
         <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA45">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AB45">
         <v>1.75</v>
@@ -7698,10 +7698,10 @@
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="P46">
         <v>1.73</v>
       </c>
       <c r="Q46">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="U46">
         <v>2.8</v>
       </c>
       <c r="V46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W46">
         <v>1.03</v>
@@ -7843,22 +7843,22 @@
         <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB46">
         <v>1.8</v>
       </c>
       <c r="AC46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
         <v>1.81</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,10 +8142,10 @@
         <v>3.5</v>
       </c>
       <c r="Q48">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="R48">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S48">
         <v>1.53</v>
@@ -8154,7 +8154,7 @@
         <v>2.32</v>
       </c>
       <c r="U48">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V48">
         <v>1.26</v>
@@ -8169,10 +8169,10 @@
         <v>1.48</v>
       </c>
       <c r="Z48">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AA48">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB48">
         <v>1.5</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="Q49">
         <v>2.39</v>
@@ -8335,7 +8335,7 @@
         <v>3</v>
       </c>
       <c r="AA49">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
         <v>1.7</v>
@@ -8350,7 +8350,7 @@
         <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG49">
         <v>1.78</v>
@@ -8631,19 +8631,19 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R51">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="S51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U51">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V51">
         <v>1.65</v>
@@ -8655,19 +8655,19 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB51">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC51">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD51">
         <v>1.67</v>
@@ -8676,10 +8676,10 @@
         <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AG51">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK51">
         <v>5.5</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
         <v>1.25</v>
@@ -2123,7 +2123,7 @@
         <v>3.5</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V11">
         <v>1.53</v>
@@ -2138,22 +2138,22 @@
         <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
         <v>1.91</v>
@@ -2175,7 +2175,7 @@
         <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G21">
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P27">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="R27">
         <v>2.25</v>
@@ -4728,19 +4728,19 @@
         <v>1.35</v>
       </c>
       <c r="T27">
-        <v>2.86</v>
+        <v>3.24</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y27">
         <v>1.25</v>
@@ -4749,19 +4749,19 @@
         <v>4</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB27">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AC27">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
         <v>1.62</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,16 +4876,16 @@
         <v>1.41</v>
       </c>
       <c r="O28">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="P28">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R28">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S28">
         <v>1.22</v>
@@ -4894,10 +4894,10 @@
         <v>3.55</v>
       </c>
       <c r="U28">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W28">
         <v>1.19</v>
@@ -4906,7 +4906,7 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -4918,19 +4918,19 @@
         <v>2.68</v>
       </c>
       <c r="AC28">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD28">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q29">
         <v>4.6</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
         <v>1.33</v>
@@ -5057,7 +5057,7 @@
         <v>2.86</v>
       </c>
       <c r="U29">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
         <v>1.4</v>
@@ -5075,10 +5075,10 @@
         <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
         <v>2.92</v>
@@ -5093,7 +5093,7 @@
         <v>1.71</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5195,56 +5195,56 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
-        <v>7.53</v>
+        <v>11.64</v>
       </c>
       <c r="O30">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Q30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T30">
         <v>3.85</v>
       </c>
       <c r="U30">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="V30">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
         <v>5.75</v>
       </c>
       <c r="AA30">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AC30">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD30">
         <v>1.7</v>
@@ -5253,7 +5253,7 @@
         <v>1.3</v>
       </c>
       <c r="AF30">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
         <v>1.75</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.11</v>
+        <v>4.06</v>
       </c>
       <c r="AK30">
         <v>1.04</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q31">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="R31">
         <v>2.22</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
         <v>2.55</v>
@@ -5395,19 +5395,19 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z31">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA31">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
         <v>1.33</v>
@@ -5416,10 +5416,10 @@
         <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
         <v>2.1</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O32">
+        <v>3.5</v>
+      </c>
+      <c r="P32">
+        <v>2.03</v>
+      </c>
+      <c r="Q32">
         <v>3.4</v>
       </c>
-      <c r="P32">
-        <v>2</v>
-      </c>
-      <c r="Q32">
-        <v>3.9</v>
-      </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC32">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AD32">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AK32">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="O33">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="V33">
         <v>1.45</v>
@@ -5727,7 +5727,7 @@
         <v>3.85</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
         <v>2</v>
@@ -5736,16 +5736,16 @@
         <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="Q34">
         <v>2.25</v>
       </c>
       <c r="R34">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
         <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
         <v>2.29</v>
@@ -5878,10 +5878,10 @@
         <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.14</v>
@@ -5896,7 +5896,7 @@
         <v>2.33</v>
       </c>
       <c r="AC34">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
         <v>1.57</v>
@@ -5905,10 +5905,10 @@
         <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
         <v>1.85</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
         <v>2.7</v>
@@ -7010,31 +7010,31 @@
         <v>1.34</v>
       </c>
       <c r="T41">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="V41">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
         <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
         <v>2.8</v>
@@ -7043,7 +7043,7 @@
         <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
         <v>1.59</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
         <v>1.44</v>
@@ -7164,22 +7164,22 @@
         <v>23.56</v>
       </c>
       <c r="Q42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R42">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T42">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="U42">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W42">
         <v>1.29</v>
@@ -7188,10 +7188,10 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z42">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA42">
         <v>1.24</v>
@@ -7200,19 +7200,19 @@
         <v>4</v>
       </c>
       <c r="AC42">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AD42">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AE42">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF42">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.12</v>
+      </c>
+      <c r="O43">
+        <v>11</v>
+      </c>
+      <c r="P43">
+        <v>12</v>
+      </c>
+      <c r="Q43">
+        <v>1.36</v>
+      </c>
+      <c r="R43">
+        <v>3.8</v>
+      </c>
+      <c r="S43">
+        <v>1.08</v>
+      </c>
+      <c r="T43">
+        <v>6.5</v>
+      </c>
+      <c r="U43">
+        <v>1.53</v>
+      </c>
+      <c r="V43">
+        <v>2.49</v>
+      </c>
+      <c r="W43">
+        <v>1.44</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.03</v>
+      </c>
+      <c r="Z43">
+        <v>15</v>
+      </c>
+      <c r="AA43">
+        <v>1.14</v>
+      </c>
+      <c r="AB43">
+        <v>5.5</v>
+      </c>
+      <c r="AC43">
+        <v>1.4</v>
+      </c>
+      <c r="AD43">
+        <v>2.9</v>
+      </c>
+      <c r="AE43">
         <v>1.91</v>
       </c>
-      <c r="O43">
-        <v>4</v>
-      </c>
-      <c r="P43">
-        <v>3.7</v>
-      </c>
-      <c r="Q43">
-        <v>2.35</v>
-      </c>
-      <c r="R43">
-        <v>2.38</v>
-      </c>
-      <c r="S43">
-        <v>1.28</v>
-      </c>
-      <c r="T43">
-        <v>3.4</v>
-      </c>
-      <c r="U43">
-        <v>2.19</v>
-      </c>
-      <c r="V43">
-        <v>1.63</v>
-      </c>
-      <c r="W43">
-        <v>1.14</v>
-      </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.14</v>
-      </c>
-      <c r="Z43">
-        <v>4.75</v>
-      </c>
-      <c r="AA43">
-        <v>1.54</v>
-      </c>
-      <c r="AB43">
-        <v>2.37</v>
-      </c>
-      <c r="AC43">
-        <v>2.4</v>
-      </c>
-      <c r="AD43">
-        <v>1.52</v>
-      </c>
-      <c r="AE43">
-        <v>1.18</v>
-      </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK43">
-        <v>1.85</v>
+        <v>7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="O44">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="P44">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="R44">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
+        <v>2.25</v>
+      </c>
+      <c r="V44">
+        <v>1.63</v>
+      </c>
+      <c r="W44">
+        <v>1.14</v>
+      </c>
+      <c r="X44">
+        <v>1.01</v>
+      </c>
+      <c r="Y44">
+        <v>1.14</v>
+      </c>
+      <c r="Z44">
+        <v>4.75</v>
+      </c>
+      <c r="AA44">
+        <v>1.61</v>
+      </c>
+      <c r="AB44">
+        <v>2.46</v>
+      </c>
+      <c r="AC44">
+        <v>2.4</v>
+      </c>
+      <c r="AD44">
+        <v>1.5</v>
+      </c>
+      <c r="AE44">
+        <v>1.22</v>
+      </c>
+      <c r="AF44">
         <v>1.53</v>
       </c>
-      <c r="V44">
-        <v>2.49</v>
-      </c>
-      <c r="W44">
-        <v>1.47</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
-      <c r="Y44">
-        <v>1.02</v>
-      </c>
-      <c r="Z44">
-        <v>15</v>
-      </c>
-      <c r="AA44">
-        <v>1.14</v>
-      </c>
-      <c r="AB44">
-        <v>5.75</v>
-      </c>
-      <c r="AC44">
-        <v>1.35</v>
-      </c>
-      <c r="AD44">
-        <v>2.9</v>
-      </c>
-      <c r="AE44">
-        <v>1.91</v>
-      </c>
-      <c r="AF44">
-        <v>1.63</v>
-      </c>
       <c r="AG44">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>7.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q50">
         <v>2.45</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,61 +1127,61 @@
         <v>1.43</v>
       </c>
       <c r="O5">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P5">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
         <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="U5">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC5">
         <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,31 +1622,31 @@
         <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R8">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T8">
         <v>3.6</v>
       </c>
       <c r="U8">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
         <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
         <v>4.65</v>
@@ -1658,13 +1658,13 @@
         <v>2.34</v>
       </c>
       <c r="AC8">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AD8">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
         <v>1.5</v>
@@ -1686,7 +1686,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
-        <v>4.59</v>
+        <v>4.9</v>
       </c>
       <c r="P11">
-        <v>7.89</v>
+        <v>7.56</v>
       </c>
       <c r="Q11">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="R11">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U11">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC11">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="P19">
-        <v>3.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q19">
-        <v>2.31</v>
+        <v>3.48</v>
       </c>
       <c r="R19">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="U19">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="P20">
-        <v>2.36</v>
+        <v>3.76</v>
       </c>
       <c r="Q20">
-        <v>3.48</v>
+        <v>2.31</v>
       </c>
       <c r="R20">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="U20">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB20">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC20">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
         <v>3.6</v>
@@ -4411,37 +4411,37 @@
         <v>1.63</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA25">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB25">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG25">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,31 +4556,31 @@
         <v>1.08</v>
       </c>
       <c r="Q26">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T26">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V26">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="W26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z26">
         <v>8</v>
@@ -4589,22 +4589,22 @@
         <v>1.3</v>
       </c>
       <c r="AB26">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AC26">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD26">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF26">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>4.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="O27">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
         <v>3.77</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA27">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="AD27">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4876,58 +4876,58 @@
         <v>1.41</v>
       </c>
       <c r="O28">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R28">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
         <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="U28">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="V28">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
         <v>1.19</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA28">
         <v>1.44</v>
       </c>
       <c r="AB28">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AC28">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AD28">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE28">
         <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,43 +5036,43 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="O29">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="AA29">
         <v>1.85</v>
@@ -5081,19 +5081,19 @@
         <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AD29">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S35">
         <v>1.39</v>
@@ -6038,13 +6038,13 @@
         <v>2.91</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.3</v>
@@ -6059,19 +6059,19 @@
         <v>1.71</v>
       </c>
       <c r="AC35">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD35">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>1.9</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="P36">
+        <v>3.7</v>
+      </c>
+      <c r="Q36">
+        <v>2.5</v>
+      </c>
+      <c r="R36">
         <v>1.91</v>
       </c>
-      <c r="O36">
-        <v>3.1</v>
-      </c>
-      <c r="P36">
-        <v>3.75</v>
-      </c>
-      <c r="Q36">
-        <v>2.63</v>
-      </c>
-      <c r="R36">
-        <v>2</v>
-      </c>
       <c r="S36">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T36">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U36">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W36">
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z36">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB36">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC36">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD36">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S37">
         <v>1.48</v>
       </c>
       <c r="T37">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U37">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="V37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.03</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y37">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z37">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="AA37">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AB37">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC37">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="AD37">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AG37">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R38">
+        <v>1.81</v>
+      </c>
+      <c r="S38">
+        <v>1.56</v>
+      </c>
+      <c r="T38">
+        <v>2.24</v>
+      </c>
+      <c r="U38">
+        <v>3.42</v>
+      </c>
+      <c r="V38">
+        <v>1.23</v>
+      </c>
+      <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
+        <v>1.1</v>
+      </c>
+      <c r="Y38">
+        <v>1.45</v>
+      </c>
+      <c r="Z38">
+        <v>2.58</v>
+      </c>
+      <c r="AA38">
+        <v>2.41</v>
+      </c>
+      <c r="AB38">
+        <v>1.49</v>
+      </c>
+      <c r="AC38">
+        <v>4.55</v>
+      </c>
+      <c r="AD38">
+        <v>1.13</v>
+      </c>
+      <c r="AE38">
+        <v>1.02</v>
+      </c>
+      <c r="AF38">
         <v>2</v>
       </c>
-      <c r="S38">
-        <v>1.49</v>
-      </c>
-      <c r="T38">
-        <v>2.51</v>
-      </c>
-      <c r="U38">
-        <v>3.3</v>
-      </c>
-      <c r="V38">
-        <v>1.29</v>
-      </c>
-      <c r="W38">
-        <v>1.03</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>1.4</v>
-      </c>
-      <c r="Z38">
-        <v>2.77</v>
-      </c>
-      <c r="AA38">
-        <v>2.34</v>
-      </c>
-      <c r="AB38">
-        <v>1.57</v>
-      </c>
-      <c r="AC38">
-        <v>4.15</v>
-      </c>
-      <c r="AD38">
-        <v>1.16</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>1.9</v>
-      </c>
       <c r="AG38">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="O39">
         <v>5.25</v>
       </c>
       <c r="P39">
-        <v>9.550000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Q39">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R39">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6693,37 +6693,37 @@
         <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA39">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
         <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
         <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AG39">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK39">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O41">
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
       </c>
       <c r="R41">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.05</v>
@@ -7031,13 +7031,13 @@
         <v>3.94</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD41">
         <v>1.4</v>
@@ -7046,10 +7046,10 @@
         <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK41">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7167,19 +7167,19 @@
         <v>1.36</v>
       </c>
       <c r="R42">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="S42">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T42">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="U42">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="V42">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="W42">
         <v>1.29</v>
@@ -7191,28 +7191,28 @@
         <v>1.06</v>
       </c>
       <c r="Z42">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC42">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AD42">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AE42">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF42">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG42">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK42">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="P43">
-        <v>12</v>
+        <v>4.02</v>
       </c>
       <c r="Q43">
-        <v>1.36</v>
+        <v>2.32</v>
       </c>
       <c r="R43">
-        <v>3.8</v>
+        <v>2.31</v>
       </c>
       <c r="S43">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
+        <v>2.32</v>
+      </c>
+      <c r="V43">
+        <v>1.63</v>
+      </c>
+      <c r="W43">
+        <v>1.14</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.14</v>
+      </c>
+      <c r="Z43">
+        <v>5</v>
+      </c>
+      <c r="AA43">
         <v>1.53</v>
       </c>
-      <c r="V43">
-        <v>2.49</v>
-      </c>
-      <c r="W43">
-        <v>1.44</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43">
-        <v>1.03</v>
-      </c>
-      <c r="Z43">
-        <v>15</v>
-      </c>
-      <c r="AA43">
-        <v>1.14</v>
-      </c>
       <c r="AB43">
-        <v>5.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC43">
-        <v>1.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD43">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG43">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>7</v>
+        <v>2.01</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="O44">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="P44">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="Q44">
-        <v>2.35</v>
+        <v>1.33</v>
       </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>4.35</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="V44">
-        <v>1.63</v>
+        <v>2.49</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
         <v>1.01</v>
       </c>
-      <c r="Y44">
-        <v>1.14</v>
-      </c>
       <c r="Z44">
-        <v>4.75</v>
+        <v>15</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="AB44">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="AC44">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="AD44">
-        <v>1.5</v>
+        <v>2.95</v>
       </c>
       <c r="AE44">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK44">
-        <v>1.85</v>
+        <v>7.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7976,28 +7976,28 @@
         <v>4.1</v>
       </c>
       <c r="P47">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q47">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T47">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U47">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="V47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,28 +8006,28 @@
         <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA47">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB47">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC47">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD47">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AK47">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -1296,25 +1296,25 @@
         <v>3.52</v>
       </c>
       <c r="Q6">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="R6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1341,7 +1341,7 @@
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG6">
         <v>1.75</v>
@@ -1360,7 +1360,7 @@
         <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="O7">
         <v>3.55</v>
       </c>
       <c r="P7">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
         <v>2.19</v>
@@ -1480,13 +1480,13 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="AA7">
         <v>1.9</v>
@@ -1495,10 +1495,10 @@
         <v>1.84</v>
       </c>
       <c r="AC7">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1969,13 +1969,13 @@
         <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
         <v>1.73</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
         <v>4.9</v>
       </c>
       <c r="P11">
-        <v>7.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="S11">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U11">
         <v>2.14</v>
@@ -2129,7 +2129,7 @@
         <v>1.66</v>
       </c>
       <c r="W11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2144,13 +2144,13 @@
         <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC11">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AD11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE11">
         <v>1.22</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>2.99</v>
+      </c>
+      <c r="R16">
+        <v>2.25</v>
+      </c>
+      <c r="S16">
+        <v>1.31</v>
+      </c>
+      <c r="T16">
+        <v>2.99</v>
+      </c>
+      <c r="U16">
+        <v>2.39</v>
+      </c>
+      <c r="V16">
+        <v>1.47</v>
+      </c>
+      <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.2</v>
+      </c>
+      <c r="Z16">
+        <v>3.7</v>
+      </c>
+      <c r="AA16">
         <v>1.76</v>
       </c>
-      <c r="O16">
-        <v>3.44</v>
-      </c>
-      <c r="P16">
-        <v>4.13</v>
-      </c>
-      <c r="Q16">
-        <v>2.69</v>
-      </c>
-      <c r="R16">
-        <v>1.96</v>
-      </c>
-      <c r="S16">
-        <v>1.39</v>
-      </c>
-      <c r="T16">
-        <v>2.64</v>
-      </c>
-      <c r="U16">
-        <v>2.8</v>
-      </c>
-      <c r="V16">
-        <v>1.35</v>
-      </c>
-      <c r="W16">
-        <v>1.05</v>
-      </c>
-      <c r="X16">
-        <v>1.02</v>
-      </c>
-      <c r="Y16">
-        <v>1.29</v>
-      </c>
-      <c r="Z16">
-        <v>3.04</v>
-      </c>
-      <c r="AA16">
-        <v>2</v>
-      </c>
       <c r="AB16">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q17">
-        <v>2.99</v>
+        <v>5.34</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
         <v>1.31</v>
       </c>
       <c r="T17">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="U17">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>2.19</v>
       </c>
       <c r="AK17">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P18">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>5.34</v>
+        <v>2.9</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,40 +3406,40 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
         <v>4.33</v>
@@ -3448,22 +3448,22 @@
         <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG19">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>3.04</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.41</v>
+        <v>2.94</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>3.12</v>
       </c>
       <c r="AA20">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AC20">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AD20">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>2.27</v>
       </c>
       <c r="R21">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AA21">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4067,25 +4067,25 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U23">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4094,25 +4094,25 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
         <v>2.1</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="R29">
         <v>2.25</v>
@@ -5072,10 +5072,10 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
         <v>1.95</v>
@@ -5205,34 +5205,34 @@
         <v>6</v>
       </c>
       <c r="P30">
+        <v>1.17</v>
+      </c>
+      <c r="Q30">
+        <v>9</v>
+      </c>
+      <c r="R30">
+        <v>2.9</v>
+      </c>
+      <c r="S30">
         <v>1.16</v>
       </c>
-      <c r="Q30">
-        <v>7</v>
-      </c>
-      <c r="R30">
-        <v>2.7</v>
-      </c>
-      <c r="S30">
-        <v>1.2</v>
-      </c>
       <c r="T30">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
         <v>5.75</v>
@@ -5244,19 +5244,19 @@
         <v>2.75</v>
       </c>
       <c r="AC30">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD30">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>4.06</v>
+        <v>5.25</v>
       </c>
       <c r="AK30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R31">
         <v>2.22</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U31">
         <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.06</v>
@@ -5395,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC31">
         <v>2.83</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q32">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5546,40 +5546,40 @@
         <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC32">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
         <v>2.3</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O33">
         <v>3.45</v>
@@ -5700,31 +5700,31 @@
         <v>3.95</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
         <v>3.05</v>
       </c>
       <c r="U33">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
         <v>1.8</v>
@@ -5733,7 +5733,7 @@
         <v>2</v>
       </c>
       <c r="AC33">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD33">
         <v>1.35</v>
@@ -5742,10 +5742,10 @@
         <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="Q34">
         <v>2.25</v>
@@ -5875,13 +5875,13 @@
         <v>2.29</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.14</v>
@@ -5893,10 +5893,10 @@
         <v>1.52</v>
       </c>
       <c r="AB34">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD34">
         <v>1.57</v>
@@ -5905,10 +5905,10 @@
         <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG34">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>1.85</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
+        <v>2.95</v>
+      </c>
+      <c r="P36">
+        <v>2.95</v>
+      </c>
+      <c r="Q36">
+        <v>3.05</v>
+      </c>
+      <c r="R36">
+        <v>1.89</v>
+      </c>
+      <c r="S36">
+        <v>1.48</v>
+      </c>
+      <c r="T36">
+        <v>2.54</v>
+      </c>
+      <c r="U36">
         <v>3</v>
-      </c>
-      <c r="P36">
-        <v>3.7</v>
-      </c>
-      <c r="Q36">
-        <v>2.5</v>
-      </c>
-      <c r="R36">
-        <v>1.91</v>
-      </c>
-      <c r="S36">
-        <v>1.45</v>
-      </c>
-      <c r="T36">
-        <v>2.45</v>
-      </c>
-      <c r="U36">
-        <v>3.04</v>
       </c>
       <c r="V36">
         <v>1.3</v>
@@ -6207,34 +6207,34 @@
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA36">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB36">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC36">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG36">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R37">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="S37">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="T37">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="U37">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
         <v>1.07</v>
       </c>
       <c r="Y37">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Z37">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AA37">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="AB37">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AC37">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AD37">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG37">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q38">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
+        <v>1.45</v>
+      </c>
+      <c r="T38">
+        <v>2.45</v>
+      </c>
+      <c r="U38">
+        <v>3.04</v>
+      </c>
+      <c r="V38">
+        <v>1.3</v>
+      </c>
+      <c r="W38">
+        <v>1.03</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.36</v>
+      </c>
+      <c r="Z38">
+        <v>2.88</v>
+      </c>
+      <c r="AA38">
+        <v>2.25</v>
+      </c>
+      <c r="AB38">
         <v>1.56</v>
       </c>
-      <c r="T38">
-        <v>2.24</v>
-      </c>
-      <c r="U38">
-        <v>3.42</v>
-      </c>
-      <c r="V38">
-        <v>1.23</v>
-      </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.1</v>
-      </c>
-      <c r="Y38">
-        <v>1.45</v>
-      </c>
-      <c r="Z38">
-        <v>2.58</v>
-      </c>
-      <c r="AA38">
-        <v>2.41</v>
-      </c>
-      <c r="AB38">
-        <v>1.49</v>
-      </c>
       <c r="AC38">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="R40">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
         <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="V40">
         <v>1.36</v>
@@ -6859,50 +6859,50 @@
         <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA40">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB40">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
+        <v>1.25</v>
+      </c>
+      <c r="AE40">
+        <v>1.04</v>
+      </c>
+      <c r="AF40">
+        <v>1.8</v>
+      </c>
+      <c r="AG40">
+        <v>1.85</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.23</v>
       </c>
-      <c r="AE40">
-        <v>1.05</v>
-      </c>
-      <c r="AF40">
-        <v>1.83</v>
-      </c>
-      <c r="AG40">
-        <v>1.86</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.24</v>
-      </c>
       <c r="AK40">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7647,40 +7647,40 @@
         <v>3.02</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q45">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
         <v>2.77</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
+        <v>1.06</v>
+      </c>
+      <c r="X45">
         <v>1.05</v>
       </c>
-      <c r="X45">
-        <v>1.01</v>
-      </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA45">
         <v>2.01</v>
@@ -7689,7 +7689,7 @@
         <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD45">
         <v>1.3</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.45</v>
+        <v>4.84</v>
       </c>
       <c r="O46">
         <v>3.71</v>
@@ -7816,49 +7816,49 @@
         <v>1.73</v>
       </c>
       <c r="Q46">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="R46">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
         <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="U46">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V46">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
         <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z46">
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB46">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
         <v>1.81</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,46 +8142,46 @@
         <v>3.5</v>
       </c>
       <c r="Q48">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S48">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T48">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="U48">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V48">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W48">
         <v>1.01</v>
       </c>
       <c r="X48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z48">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AA48">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB48">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC48">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
         <v>1.05</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
         <v>1.73</v>
@@ -8299,13 +8299,13 @@
         <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>4.37</v>
+        <v>4</v>
       </c>
       <c r="Q49">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
         <v>2.05</v>
@@ -8332,22 +8332,22 @@
         <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA49">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB49">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC49">
         <v>3.8</v>
       </c>
       <c r="AD49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
         <v>1.91</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK49">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8465,7 +8465,7 @@
         <v>3.35</v>
       </c>
       <c r="P50">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q50">
         <v>2.45</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
         <v>1.65</v>
@@ -8631,56 +8631,56 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R51">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="S51">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="U51">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V51">
         <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA51">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD51">
+        <v>1.72</v>
+      </c>
+      <c r="AE51">
+        <v>1.28</v>
+      </c>
+      <c r="AF51">
+        <v>2.23</v>
+      </c>
+      <c r="AG51">
         <v>1.67</v>
       </c>
-      <c r="AE51">
-        <v>1.25</v>
-      </c>
-      <c r="AF51">
-        <v>2.2</v>
-      </c>
-      <c r="AG51">
-        <v>1.62</v>
-      </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
+        <v>1.22</v>
+      </c>
+      <c r="T4">
+        <v>3.9</v>
+      </c>
+      <c r="U4">
+        <v>2.21</v>
+      </c>
+      <c r="V4">
+        <v>1.65</v>
+      </c>
+      <c r="W4">
+        <v>1.14</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.09</v>
+      </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
+      <c r="AA4">
+        <v>1.44</v>
+      </c>
+      <c r="AB4">
+        <v>2.6</v>
+      </c>
+      <c r="AC4">
+        <v>2.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.65</v>
+      </c>
+      <c r="AE4">
         <v>1.21</v>
       </c>
-      <c r="T4">
-        <v>3.58</v>
-      </c>
-      <c r="U4">
-        <v>2.02</v>
-      </c>
-      <c r="V4">
-        <v>1.7</v>
-      </c>
-      <c r="W4">
-        <v>1.16</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.07</v>
-      </c>
-      <c r="Z4">
-        <v>5.8</v>
-      </c>
-      <c r="AA4">
-        <v>1.34</v>
-      </c>
-      <c r="AB4">
-        <v>2.78</v>
-      </c>
-      <c r="AC4">
-        <v>1.9</v>
-      </c>
-      <c r="AD4">
-        <v>1.8</v>
-      </c>
-      <c r="AE4">
-        <v>1.31</v>
-      </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T5">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
+        <v>1.7</v>
+      </c>
+      <c r="W5">
+        <v>1.16</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1.07</v>
+      </c>
+      <c r="Z5">
+        <v>5.8</v>
+      </c>
+      <c r="AA5">
+        <v>1.34</v>
+      </c>
+      <c r="AB5">
+        <v>2.78</v>
+      </c>
+      <c r="AC5">
+        <v>1.9</v>
+      </c>
+      <c r="AD5">
+        <v>1.8</v>
+      </c>
+      <c r="AE5">
+        <v>1.31</v>
+      </c>
+      <c r="AF5">
         <v>1.65</v>
       </c>
-      <c r="W5">
-        <v>1.14</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
+      <c r="AG5">
+        <v>2.1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.09</v>
       </c>
-      <c r="Z5">
-        <v>6</v>
-      </c>
-      <c r="AA5">
-        <v>1.44</v>
-      </c>
-      <c r="AB5">
-        <v>2.6</v>
-      </c>
-      <c r="AC5">
-        <v>2.2</v>
-      </c>
-      <c r="AD5">
-        <v>1.65</v>
-      </c>
-      <c r="AE5">
-        <v>1.21</v>
-      </c>
-      <c r="AF5">
-        <v>1.57</v>
-      </c>
-      <c r="AG5">
-        <v>2.25</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.14</v>
-      </c>
       <c r="AK5">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="R20">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="U20">
-        <v>2.94</v>
+        <v>2.42</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
-        <v>3.12</v>
+        <v>4.5</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="V21">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD21">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AG21">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U27">
         <v>2.55</v>
@@ -4761,7 +4761,7 @@
         <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
         <v>1.58</v>
@@ -4876,7 +4876,7 @@
         <v>1.41</v>
       </c>
       <c r="O28">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -4891,13 +4891,13 @@
         <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="U28">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W28">
         <v>1.19</v>
@@ -4915,10 +4915,10 @@
         <v>1.44</v>
       </c>
       <c r="AB28">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC28">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AD28">
         <v>1.7</v>
@@ -4927,7 +4927,7 @@
         <v>1.28</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6023,7 +6023,7 @@
         <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R35">
         <v>2.09</v>
@@ -6044,13 +6044,13 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA35">
         <v>2.02</v>
@@ -6059,7 +6059,7 @@
         <v>1.71</v>
       </c>
       <c r="AC35">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
         <v>1.25</v>
@@ -6068,10 +6068,10 @@
         <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG35">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -7013,10 +7013,10 @@
         <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
         <v>1.11</v>
@@ -7164,7 +7164,7 @@
         <v>23.56</v>
       </c>
       <c r="Q42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R42">
         <v>3.43</v>
@@ -7173,10 +7173,10 @@
         <v>1.13</v>
       </c>
       <c r="T42">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="U42">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V42">
         <v>1.95</v>
@@ -7191,19 +7191,19 @@
         <v>1.06</v>
       </c>
       <c r="Z42">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB42">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AC42">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD42">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AE42">
         <v>1.55</v>
@@ -7321,7 +7321,7 @@
         <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P43">
         <v>4.02</v>
@@ -7357,7 +7357,7 @@
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB43">
         <v>2.29</v>
@@ -7490,7 +7490,7 @@
         <v>12</v>
       </c>
       <c r="Q44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R44">
         <v>4.35</v>
@@ -7502,10 +7502,10 @@
         <v>5.7</v>
       </c>
       <c r="U44">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V44">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="W44">
         <v>1.48</v>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z44">
         <v>15</v>
@@ -7523,13 +7523,13 @@
         <v>1.09</v>
       </c>
       <c r="AB44">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC44">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AE44">
         <v>1.93</v>
@@ -7538,7 +7538,7 @@
         <v>1.65</v>
       </c>
       <c r="AG44">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.03</v>
       </c>
       <c r="AK44">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>4.84</v>
       </c>
       <c r="O46">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
         <v>1.73</v>
@@ -7819,7 +7819,7 @@
         <v>5.25</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
         <v>1.38</v>
@@ -7837,7 +7837,7 @@
         <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.29</v>
@@ -7846,7 +7846,7 @@
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB46">
         <v>1.79</v>
@@ -7855,16 +7855,16 @@
         <v>3.4</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG46">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O47">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P47">
         <v>7</v>
@@ -7988,7 +7988,7 @@
         <v>1.41</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
         <v>2.94</v>
@@ -7997,13 +7997,13 @@
         <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z47">
         <v>3.04</v>
@@ -8462,7 +8462,7 @@
         <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
         <v>3.3</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -6023,16 +6023,16 @@
         <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="R35">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U35">
         <v>2.91</v>
@@ -6044,34 +6044,34 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
         <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
         <v>1.74</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q37">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S37">
+        <v>1.45</v>
+      </c>
+      <c r="T37">
+        <v>2.45</v>
+      </c>
+      <c r="U37">
+        <v>3.04</v>
+      </c>
+      <c r="V37">
+        <v>1.3</v>
+      </c>
+      <c r="W37">
+        <v>1.03</v>
+      </c>
+      <c r="X37">
+        <v>1.05</v>
+      </c>
+      <c r="Y37">
+        <v>1.36</v>
+      </c>
+      <c r="Z37">
+        <v>2.88</v>
+      </c>
+      <c r="AA37">
+        <v>2.25</v>
+      </c>
+      <c r="AB37">
         <v>1.56</v>
       </c>
-      <c r="T37">
-        <v>2.55</v>
-      </c>
-      <c r="U37">
-        <v>3.42</v>
-      </c>
-      <c r="V37">
-        <v>1.23</v>
-      </c>
-      <c r="W37">
-        <v>1.05</v>
-      </c>
-      <c r="X37">
-        <v>1.07</v>
-      </c>
-      <c r="Y37">
-        <v>1.45</v>
-      </c>
-      <c r="Z37">
-        <v>2.58</v>
-      </c>
-      <c r="AA37">
-        <v>2.41</v>
-      </c>
-      <c r="AB37">
-        <v>1.49</v>
-      </c>
       <c r="AC37">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG37">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S38">
+        <v>1.56</v>
+      </c>
+      <c r="T38">
+        <v>2.55</v>
+      </c>
+      <c r="U38">
+        <v>3.42</v>
+      </c>
+      <c r="V38">
+        <v>1.23</v>
+      </c>
+      <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
+        <v>1.07</v>
+      </c>
+      <c r="Y38">
         <v>1.45</v>
       </c>
-      <c r="T38">
-        <v>2.45</v>
-      </c>
-      <c r="U38">
-        <v>3.04</v>
-      </c>
-      <c r="V38">
-        <v>1.3</v>
-      </c>
-      <c r="W38">
-        <v>1.03</v>
-      </c>
-      <c r="X38">
-        <v>1.05</v>
-      </c>
-      <c r="Y38">
-        <v>1.36</v>
-      </c>
       <c r="Z38">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AA38">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB38">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AC38">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD38">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG38">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>1.4</v>
       </c>
       <c r="O47">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P47">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q47">
         <v>1.96</v>
       </c>
       <c r="R47">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
         <v>1.41</v>
@@ -7997,13 +7997,13 @@
         <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
         <v>3.04</v>
@@ -8024,10 +8024,10 @@
         <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG47">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P48">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q48">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="R48">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S48">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T48">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U48">
         <v>3.35</v>
@@ -8163,25 +8163,25 @@
         <v>1.01</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y48">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z48">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AA48">
         <v>2.45</v>
       </c>
       <c r="AB48">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC48">
         <v>4.4</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE48">
         <v>1.05</v>
@@ -8190,7 +8190,7 @@
         <v>2.1</v>
       </c>
       <c r="AG48">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK48">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,25 +8299,25 @@
         <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R49">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="U49">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V49">
         <v>1.36</v>
@@ -8329,25 +8329,25 @@
         <v>1.06</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z49">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC49">
         <v>3.8</v>
       </c>
       <c r="AD49">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
         <v>1.91</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
         <v>1.97</v>
@@ -8465,7 +8465,7 @@
         <v>3.25</v>
       </c>
       <c r="P50">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q50">
         <v>2.45</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
         <v>1.65</v>
@@ -8631,25 +8631,25 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S51">
         <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U51">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="V51">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,25 +8658,25 @@
         <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA51">
         <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC51">
         <v>2.1</v>
       </c>
       <c r="AD51">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE51">
         <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AG51">
         <v>1.67</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK51">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -644,31 +644,31 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
         <v>3.4</v>
@@ -680,7 +680,7 @@
         <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD2">
         <v>1.3</v>
@@ -692,7 +692,7 @@
         <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="P3">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>1.43</v>
       </c>
       <c r="O4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q4">
         <v>1.91</v>
@@ -979,10 +979,10 @@
         <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U4">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="V4">
         <v>1.65</v>
@@ -994,13 +994,13 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB4">
         <v>2.6</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T5">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V5">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z5">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AB5">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AD5">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AE5">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1622,49 +1622,49 @@
         <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R8">
         <v>2.45</v>
       </c>
       <c r="S8">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="AA8">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB8">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF8">
         <v>1.5</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.69</v>
+        <v>3.82</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2268,40 +2268,40 @@
         <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
@@ -2310,19 +2310,19 @@
         <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG12">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="P22">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="Q22">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z22">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AB22">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AG22">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O24">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P24">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q24">
         <v>3</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U24">
         <v>2.97</v>
@@ -4251,34 +4251,34 @@
         <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
         <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC24">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG24">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P25">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="Q25">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R25">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S25">
         <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U25">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W25">
         <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA25">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG25">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,19 +4559,19 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S26">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="U26">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V26">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="W26">
         <v>1.25</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z26">
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AB26">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AC26">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD26">
         <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.07</v>
+        <v>4.2</v>
       </c>
       <c r="AK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>11.64</v>
+        <v>13</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P30">
+        <v>1.2</v>
+      </c>
+      <c r="Q30">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="R30">
+        <v>2.67</v>
+      </c>
+      <c r="S30">
         <v>1.17</v>
       </c>
-      <c r="Q30">
-        <v>9</v>
-      </c>
-      <c r="R30">
+      <c r="T30">
         <v>2.9</v>
       </c>
-      <c r="S30">
-        <v>1.16</v>
-      </c>
-      <c r="T30">
-        <v>3</v>
-      </c>
       <c r="U30">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V30">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="W30">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB30">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC30">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AD30">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF30">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>5.25</v>
+        <v>4.54</v>
       </c>
       <c r="AK30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6023,16 +6023,16 @@
         <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T35">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U35">
         <v>2.91</v>
@@ -6053,7 +6053,7 @@
         <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB35">
         <v>1.72</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O36">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P36">
         <v>2.95</v>
       </c>
       <c r="Q36">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
         <v>1.89</v>
@@ -6219,16 +6219,16 @@
         <v>2.28</v>
       </c>
       <c r="AB36">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC36">
         <v>4.05</v>
       </c>
       <c r="AD36">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
         <v>1.88</v>
@@ -6250,7 +6250,7 @@
         <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O37">
         <v>3</v>
       </c>
       <c r="P37">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q37">
         <v>2.5</v>
@@ -6355,10 +6355,10 @@
         <v>1.91</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U37">
         <v>3.04</v>
@@ -6367,7 +6367,7 @@
         <v>1.3</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.05</v>
@@ -6391,13 +6391,13 @@
         <v>1.17</v>
       </c>
       <c r="AE37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG37">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>1.56</v>
       </c>
       <c r="T38">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="U38">
         <v>3.42</v>
@@ -6539,16 +6539,16 @@
         <v>1.45</v>
       </c>
       <c r="Z38">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AA38">
         <v>2.41</v>
       </c>
       <c r="AB38">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC38">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD38">
         <v>1.13</v>
@@ -6557,10 +6557,10 @@
         <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="O39">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P39">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q39">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R39">
         <v>2.45</v>
@@ -6684,7 +6684,7 @@
         <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6699,28 +6699,28 @@
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z39">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AA39">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC39">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG39">
         <v>1.57</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK39">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="V40">
         <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z40">
         <v>2.97</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC40">
         <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
         <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -7659,43 +7659,43 @@
         <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T45">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="U45">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W45">
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="AA45">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB45">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC45">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
         <v>1.75</v>
@@ -7810,22 +7810,22 @@
         <v>4.84</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="P46">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="Q46">
         <v>5.25</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
         <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="U46">
         <v>2.65</v>
@@ -7846,25 +7846,25 @@
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC46">
         <v>3.4</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O47">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q47">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
         <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
         <v>2.88</v>
       </c>
       <c r="U47">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
         <v>1.07</v>
@@ -8043,7 +8043,7 @@
         <v>1.01</v>
       </c>
       <c r="AK47">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -1296,19 +1296,19 @@
         <v>3.52</v>
       </c>
       <c r="Q6">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="R6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V6">
         <v>1.3</v>
@@ -1320,19 +1320,19 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AA6">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="AD6">
         <v>1.18</v>
@@ -1341,7 +1341,7 @@
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
         <v>1.75</v>
@@ -1360,7 +1360,7 @@
         <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q7">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
         <v>1.33</v>
@@ -1471,10 +1471,10 @@
         <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.08</v>
@@ -1483,28 +1483,28 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
         <v>1.85</v>
@@ -1523,7 +1523,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1945,49 +1945,49 @@
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q10">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="R10">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
         <v>1.1</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AK10">
         <v>1.36</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.36</v>
+      </c>
+      <c r="O11">
+        <v>4.5</v>
+      </c>
+      <c r="P11">
+        <v>5.8</v>
+      </c>
+      <c r="Q11">
+        <v>1.75</v>
+      </c>
+      <c r="R11">
+        <v>2.5</v>
+      </c>
+      <c r="S11">
         <v>1.25</v>
       </c>
-      <c r="O11">
-        <v>4.9</v>
-      </c>
-      <c r="P11">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q11">
-        <v>1.72</v>
-      </c>
-      <c r="R11">
-        <v>2.59</v>
-      </c>
-      <c r="S11">
-        <v>1.23</v>
-      </c>
       <c r="T11">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V11">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,25 +2141,25 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC11">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AD11">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK11">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>2.62</v>
@@ -2304,10 +2304,10 @@
         <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
         <v>3.2</v>
@@ -2926,71 +2926,71 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC16">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
+        <v>1.62</v>
+      </c>
+      <c r="AG16">
+        <v>2.15</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.31</v>
+      </c>
+      <c r="AK16">
         <v>1.57</v>
-      </c>
-      <c r="AG16">
-        <v>2.25</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.43</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,77 +3080,77 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q17">
-        <v>5.34</v>
+        <v>5.13</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="U17">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
+        <v>1.95</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>2.19</v>
       </c>
       <c r="AK17">
         <v>1.13</v>
@@ -3246,7 +3246,7 @@
         <v>2.5</v>
       </c>
       <c r="O18">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
         <v>2.3</v>
@@ -3267,7 +3267,7 @@
         <v>2.36</v>
       </c>
       <c r="V18">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
         <v>1.12</v>
@@ -3285,7 +3285,7 @@
         <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
         <v>2.35</v>
@@ -3300,7 +3300,7 @@
         <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S19">
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
         <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
         <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB19">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
         <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE19">
         <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q20">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC20">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AG20">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q21">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="R21">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>3.04</v>
       </c>
       <c r="U21">
-        <v>2.94</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>3.12</v>
+        <v>3.98</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AC21">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
         <v>3.15</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
         <v>1.41</v>
@@ -4094,28 +4094,28 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4713,31 +4713,31 @@
         <v>3.24</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
         <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
         <v>3.18</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4749,25 +4749,25 @@
         <v>3.84</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
         <v>1.58</v>
       </c>
       <c r="AG27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="O28">
-        <v>5.1</v>
+        <v>4.94</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="Q28">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W28">
         <v>1.19</v>
@@ -4909,28 +4909,28 @@
         <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA28">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB28">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC28">
         <v>2.08</v>
       </c>
       <c r="AD28">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,37 +5036,37 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q29">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V29">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
@@ -5075,19 +5075,19 @@
         <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
         <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
         <v>1.6</v>
@@ -5362,52 +5362,52 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="U31">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
         <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
         <v>1.33</v>
@@ -5419,7 +5419,7 @@
         <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,31 +5534,31 @@
         <v>2.05</v>
       </c>
       <c r="Q32">
-        <v>3.13</v>
+        <v>3.44</v>
       </c>
       <c r="R32">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U32">
         <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
         <v>4.2</v>
@@ -5567,10 +5567,10 @@
         <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AC32">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD32">
         <v>1.44</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,58 +5694,58 @@
         <v>3.45</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q33">
-        <v>3.95</v>
+        <v>4.19</v>
       </c>
       <c r="R33">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA33">
         <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
         <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q34">
         <v>2.25</v>
       </c>
       <c r="R34">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5878,13 +5878,13 @@
         <v>1.58</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
         <v>4.9</v>
@@ -5893,13 +5893,13 @@
         <v>1.52</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC34">
         <v>2.28</v>
       </c>
       <c r="AD34">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE34">
         <v>1.18</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="O41">
+        <v>6.52</v>
+      </c>
+      <c r="P41">
+        <v>23.56</v>
+      </c>
+      <c r="Q41">
+        <v>1.36</v>
+      </c>
+      <c r="R41">
         <v>3.5</v>
       </c>
-      <c r="P41">
-        <v>2.65</v>
-      </c>
-      <c r="Q41">
-        <v>3.1</v>
-      </c>
-      <c r="R41">
+      <c r="S41">
+        <v>1.1</v>
+      </c>
+      <c r="T41">
+        <v>5.2</v>
+      </c>
+      <c r="U41">
+        <v>1.72</v>
+      </c>
+      <c r="V41">
+        <v>1.97</v>
+      </c>
+      <c r="W41">
+        <v>1.3</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.06</v>
+      </c>
+      <c r="Z41">
+        <v>10</v>
+      </c>
+      <c r="AA41">
+        <v>1.22</v>
+      </c>
+      <c r="AB41">
+        <v>4</v>
+      </c>
+      <c r="AC41">
+        <v>1.62</v>
+      </c>
+      <c r="AD41">
         <v>2.25</v>
       </c>
-      <c r="S41">
-        <v>1.35</v>
-      </c>
-      <c r="T41">
-        <v>3.1</v>
-      </c>
-      <c r="U41">
-        <v>2.67</v>
-      </c>
-      <c r="V41">
-        <v>1.47</v>
-      </c>
-      <c r="W41">
-        <v>1.11</v>
-      </c>
-      <c r="X41">
-        <v>1.05</v>
-      </c>
-      <c r="Y41">
-        <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.94</v>
-      </c>
-      <c r="AA41">
-        <v>1.75</v>
-      </c>
-      <c r="AB41">
-        <v>2</v>
-      </c>
-      <c r="AC41">
-        <v>2.9</v>
-      </c>
-      <c r="AD41">
-        <v>1.4</v>
-      </c>
       <c r="AE41">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AG41">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AK41">
-        <v>1.55</v>
+        <v>6.7</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="O42">
-        <v>6.52</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>23.56</v>
+        <v>4.02</v>
       </c>
       <c r="Q42">
-        <v>1.33</v>
+        <v>2.34</v>
       </c>
       <c r="R42">
-        <v>3.43</v>
+        <v>2.26</v>
       </c>
       <c r="S42">
+        <v>1.22</v>
+      </c>
+      <c r="T42">
+        <v>3.6</v>
+      </c>
+      <c r="U42">
+        <v>2.32</v>
+      </c>
+      <c r="V42">
+        <v>1.63</v>
+      </c>
+      <c r="W42">
         <v>1.13</v>
-      </c>
-      <c r="T42">
-        <v>5.3</v>
-      </c>
-      <c r="U42">
-        <v>1.73</v>
-      </c>
-      <c r="V42">
-        <v>1.95</v>
-      </c>
-      <c r="W42">
-        <v>1.29</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>4.25</v>
+        <v>2.54</v>
       </c>
       <c r="AC42">
+        <v>2.45</v>
+      </c>
+      <c r="AD42">
         <v>1.6</v>
       </c>
-      <c r="AD42">
-        <v>2.33</v>
-      </c>
       <c r="AE42">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>4.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q43">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="R43">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U43">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="V43">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA43">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB43">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AC43">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AK43">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,28 +7487,28 @@
         <v>11</v>
       </c>
       <c r="P44">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q44">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R44">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="S44">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T44">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="U44">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="V44">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="W44">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -7517,28 +7517,28 @@
         <v>1.03</v>
       </c>
       <c r="Z44">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA44">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AB44">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AC44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD44">
         <v>3</v>
       </c>
       <c r="AE44">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF44">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.03</v>
       </c>
       <c r="AK44">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7650,25 +7650,25 @@
         <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q45">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S45">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U45">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7677,31 +7677,31 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB45">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC45">
         <v>3.2</v>
       </c>
       <c r="AD45">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
         <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK45">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O48">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q48">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U48">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="V48">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AA48">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC48">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD48">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE48">
         <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q49">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="T49">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="U49">
-        <v>2.82</v>
+        <v>3.36</v>
       </c>
       <c r="V49">
+        <v>1.25</v>
+      </c>
+      <c r="W49">
+        <v>1.01</v>
+      </c>
+      <c r="X49">
+        <v>1.11</v>
+      </c>
+      <c r="Y49">
+        <v>1.5</v>
+      </c>
+      <c r="Z49">
+        <v>2.65</v>
+      </c>
+      <c r="AA49">
+        <v>2.32</v>
+      </c>
+      <c r="AB49">
+        <v>1.5</v>
+      </c>
+      <c r="AC49">
+        <v>4.75</v>
+      </c>
+      <c r="AD49">
+        <v>1.18</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>2.05</v>
+      </c>
+      <c r="AG49">
+        <v>1.7</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.36</v>
       </c>
-      <c r="W49">
-        <v>1.05</v>
-      </c>
-      <c r="X49">
-        <v>1.06</v>
-      </c>
-      <c r="Y49">
-        <v>1.32</v>
-      </c>
-      <c r="Z49">
-        <v>3</v>
-      </c>
-      <c r="AA49">
-        <v>2.05</v>
-      </c>
-      <c r="AB49">
+      <c r="AK49">
         <v>1.7</v>
-      </c>
-      <c r="AC49">
-        <v>3.8</v>
-      </c>
-      <c r="AD49">
-        <v>1.22</v>
-      </c>
-      <c r="AE49">
-        <v>1.08</v>
-      </c>
-      <c r="AF49">
-        <v>1.91</v>
-      </c>
-      <c r="AG49">
-        <v>1.78</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.13</v>
-      </c>
-      <c r="AK49">
-        <v>1.97</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q50">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U50">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V50">
         <v>1.42</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
         <v>1.91</v>
       </c>
       <c r="AC50">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
         <v>2.1</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8637,13 +8637,13 @@
         <v>3.1</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V51">
         <v>1.7</v>
@@ -8655,10 +8655,10 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA51">
         <v>1.44</v>
@@ -8670,16 +8670,16 @@
         <v>2.1</v>
       </c>
       <c r="AD51">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE51">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF51">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG51">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S4">
+        <v>1.19</v>
+      </c>
+      <c r="T4">
+        <v>4.6</v>
+      </c>
+      <c r="U4">
+        <v>1.92</v>
+      </c>
+      <c r="V4">
+        <v>1.78</v>
+      </c>
+      <c r="W4">
         <v>1.22</v>
       </c>
-      <c r="T4">
-        <v>3.85</v>
-      </c>
-      <c r="U4">
-        <v>2.07</v>
-      </c>
-      <c r="V4">
-        <v>1.65</v>
-      </c>
-      <c r="W4">
-        <v>1.14</v>
-      </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AB4">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC4">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AD4">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK4">
-        <v>2.36</v>
+        <v>1.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="V5">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AB5">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC5">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>1.06</v>
+        <v>2.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.95</v>
+        <v>1.43</v>
       </c>
       <c r="O13">
-        <v>2.55</v>
+        <v>3.86</v>
       </c>
       <c r="P13">
-        <v>2.29</v>
+        <v>6.62</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.43</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>6.62</v>
+        <v>1.42</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="P15">
-        <v>1.42</v>
+        <v>2.29</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
@@ -6029,49 +6029,49 @@
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T35">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="U35">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC35">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
         <v>7</v>
       </c>
       <c r="Q47">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="S47">
+        <v>1.44</v>
+      </c>
+      <c r="T47">
+        <v>2.63</v>
+      </c>
+      <c r="U47">
+        <v>3.25</v>
+      </c>
+      <c r="V47">
+        <v>1.27</v>
+      </c>
+      <c r="W47">
+        <v>1.04</v>
+      </c>
+      <c r="X47">
+        <v>1.04</v>
+      </c>
+      <c r="Y47">
+        <v>1.4</v>
+      </c>
+      <c r="Z47">
+        <v>2.57</v>
+      </c>
+      <c r="AA47">
+        <v>2.27</v>
+      </c>
+      <c r="AB47">
+        <v>1.56</v>
+      </c>
+      <c r="AC47">
+        <v>4.15</v>
+      </c>
+      <c r="AD47">
+        <v>1.13</v>
+      </c>
+      <c r="AE47">
+        <v>1.01</v>
+      </c>
+      <c r="AF47">
+        <v>2.15</v>
+      </c>
+      <c r="AG47">
         <v>1.36</v>
       </c>
-      <c r="T47">
-        <v>2.88</v>
-      </c>
-      <c r="U47">
-        <v>2.91</v>
-      </c>
-      <c r="V47">
-        <v>1.33</v>
-      </c>
-      <c r="W47">
-        <v>1.07</v>
-      </c>
-      <c r="X47">
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.02</v>
       </c>
-      <c r="Y47">
-        <v>1.25</v>
-      </c>
-      <c r="Z47">
-        <v>3.04</v>
-      </c>
-      <c r="AA47">
-        <v>1.99</v>
-      </c>
-      <c r="AB47">
-        <v>1.73</v>
-      </c>
-      <c r="AC47">
-        <v>3.34</v>
-      </c>
-      <c r="AD47">
-        <v>1.24</v>
-      </c>
-      <c r="AE47">
-        <v>1.08</v>
-      </c>
-      <c r="AF47">
-        <v>2</v>
-      </c>
-      <c r="AG47">
-        <v>1.44</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.01</v>
-      </c>
       <c r="AK47">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -627,45 +627,45 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="U2">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
         <v>1.06</v>
-      </c>
-      <c r="X2">
-        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -674,68 +674,68 @@
         <v>3.4</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
+        <v>1.91</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>["90+3"]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.33</v>
+      </c>
+      <c r="AK2">
+        <v>1.36</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
         <v>2</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.53</v>
-      </c>
-      <c r="AK2">
-        <v>1.26</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>-1</v>
-      </c>
-      <c r="AN2">
-        <v>-1</v>
-      </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="V4">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W4">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA4">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AB4">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC4">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AE4">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>1.06</v>
+        <v>2.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S5">
+        <v>1.19</v>
+      </c>
+      <c r="T5">
+        <v>4.6</v>
+      </c>
+      <c r="U5">
+        <v>1.92</v>
+      </c>
+      <c r="V5">
+        <v>1.78</v>
+      </c>
+      <c r="W5">
         <v>1.22</v>
       </c>
-      <c r="T5">
-        <v>3.85</v>
-      </c>
-      <c r="U5">
-        <v>2.07</v>
-      </c>
-      <c r="V5">
-        <v>1.65</v>
-      </c>
-      <c r="W5">
-        <v>1.14</v>
-      </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AB5">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>2.36</v>
+        <v>1.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="P6">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U6">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AA6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC6">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA7">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
         <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
+        <v>1.9</v>
+      </c>
+      <c r="AC10">
+        <v>2.92</v>
+      </c>
+      <c r="AD10">
+        <v>1.31</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>1.63</v>
+      </c>
+      <c r="AG10">
         <v>2.06</v>
       </c>
-      <c r="AC10">
-        <v>2.81</v>
-      </c>
-      <c r="AD10">
-        <v>1.4</v>
-      </c>
-      <c r="AE10">
-        <v>1.1</v>
-      </c>
-      <c r="AF10">
-        <v>1.57</v>
-      </c>
-      <c r="AG10">
-        <v>2.2</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R37">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="T37">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="U37">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y37">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AA37">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB37">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC37">
         <v>4.5</v>
       </c>
       <c r="AD37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE37">
         <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG37">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
+        <v>1.4</v>
+      </c>
+      <c r="T38">
+        <v>2.6</v>
+      </c>
+      <c r="U38">
+        <v>3.04</v>
+      </c>
+      <c r="V38">
+        <v>1.3</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.36</v>
+      </c>
+      <c r="Z38">
+        <v>2.88</v>
+      </c>
+      <c r="AA38">
+        <v>2.25</v>
+      </c>
+      <c r="AB38">
         <v>1.56</v>
-      </c>
-      <c r="T38">
-        <v>2.24</v>
-      </c>
-      <c r="U38">
-        <v>3.42</v>
-      </c>
-      <c r="V38">
-        <v>1.23</v>
-      </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.07</v>
-      </c>
-      <c r="Y38">
-        <v>1.45</v>
-      </c>
-      <c r="Z38">
-        <v>2.46</v>
-      </c>
-      <c r="AA38">
-        <v>2.41</v>
-      </c>
-      <c r="AB38">
-        <v>1.5</v>
       </c>
       <c r="AC38">
         <v>4.5</v>
       </c>
       <c r="AD38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE38">
         <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG38">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.4</v>
+        <v>1.13</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="P43">
-        <v>2.65</v>
+        <v>20</v>
       </c>
       <c r="Q43">
-        <v>3.25</v>
+        <v>1.31</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="S43">
+        <v>1.05</v>
+      </c>
+      <c r="T43">
+        <v>8</v>
+      </c>
+      <c r="U43">
+        <v>1.43</v>
+      </c>
+      <c r="V43">
+        <v>2.6</v>
+      </c>
+      <c r="W43">
+        <v>1.54</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>1.03</v>
+      </c>
+      <c r="Z43">
+        <v>17</v>
+      </c>
+      <c r="AA43">
+        <v>1.12</v>
+      </c>
+      <c r="AB43">
+        <v>6</v>
+      </c>
+      <c r="AC43">
         <v>1.3</v>
       </c>
-      <c r="T43">
-        <v>3.15</v>
-      </c>
-      <c r="U43">
-        <v>2.57</v>
-      </c>
-      <c r="V43">
-        <v>1.5</v>
-      </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1.05</v>
-      </c>
-      <c r="Y43">
-        <v>1.22</v>
-      </c>
-      <c r="Z43">
-        <v>4</v>
-      </c>
-      <c r="AA43">
-        <v>1.75</v>
-      </c>
-      <c r="AB43">
-        <v>2.05</v>
-      </c>
-      <c r="AC43">
-        <v>2.9</v>
-      </c>
       <c r="AD43">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>6.1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="O44">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>20</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="R44">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
+        <v>1.3</v>
+      </c>
+      <c r="T44">
+        <v>3.15</v>
+      </c>
+      <c r="U44">
+        <v>2.57</v>
+      </c>
+      <c r="V44">
+        <v>1.5</v>
+      </c>
+      <c r="W44">
+        <v>1.08</v>
+      </c>
+      <c r="X44">
         <v>1.05</v>
       </c>
-      <c r="T44">
-        <v>8</v>
-      </c>
-      <c r="U44">
-        <v>1.43</v>
-      </c>
-      <c r="V44">
-        <v>2.6</v>
-      </c>
-      <c r="W44">
-        <v>1.54</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
       <c r="Y44">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AA44">
-        <v>1.12</v>
+        <v>1.75</v>
       </c>
       <c r="AB44">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="AC44">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD44">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AK44">
-        <v>6.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-09-10.xlsx
+++ b/jogos_2026-09-10.xlsx
@@ -775,130 +775,130 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA3">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "61"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -953,24 +953,24 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R4">
         <v>2.5</v>
@@ -979,13 +979,13 @@
         <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="U4">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
         <v>1.14</v>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB4">
         <v>2.6</v>
@@ -1012,56 +1012,56 @@
         <v>1.65</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF4">
         <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1113,118 +1113,118 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="R5">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="S5">
         <v>1.19</v>
       </c>
       <c r="T5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V5">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>5.98</v>
       </c>
       <c r="AA5">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AB5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC5">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE5">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AF5">
         <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ5">
         <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "90+2"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,14 +1439,14 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1622,22 +1622,22 @@
         <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="R8">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T8">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U8">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="V8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W8">
         <v>1.14</v>
@@ -1646,25 +1646,25 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA8">
         <v>1.47</v>
       </c>
       <c r="AB8">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC8">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD8">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE8">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF8">
         <v>1.5</v>
@@ -1674,34 +1674,34 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1772,111 +1772,111 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
         <v>3.82</v>
       </c>
       <c r="O9">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P9">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2108,25 +2108,25 @@
         <v>4.5</v>
       </c>
       <c r="P11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T11">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W11">
         <v>1.14</v>
@@ -2138,71 +2138,71 @@
         <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA11">
         <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AC11">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD11">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
         <v>1.19</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
+        <v>1.91</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.13</v>
+      </c>
+      <c r="AK11">
+        <v>2.88</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>5</v>
+      </c>
+      <c r="AN11">
         <v>2</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.08</v>
-      </c>
-      <c r="AK11">
-        <v>2.9</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-1</v>
-      </c>
-      <c r="AN11">
-        <v>-1</v>
-      </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,29 +2261,29 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
         <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
         <v>2.75</v>
@@ -2298,40 +2298,40 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2417,91 +2417,91 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O13">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>6.62</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>["75"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,88 +2580,88 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P14">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["54"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -2731,103 +2731,103 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O15">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="P15">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "87"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "28", "42"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2913,38 +2913,38 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,68 +2956,68 @@
         <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>["10", "27"]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ16">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,139 +3048,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>4.33</v>
+        <v>1.84</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>1.65</v>
+        <v>3.61</v>
       </c>
       <c r="Q17">
-        <v>5.13</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
         <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "41", "87"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "64", "81"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,139 +3211,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>2.9</v>
+        <v>5.65</v>
       </c>
       <c r="R18">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U18">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC18">
+        <v>2.52</v>
+      </c>
+      <c r="AD18">
+        <v>1.4</v>
+      </c>
+      <c r="AE18">
+        <v>1.17</v>
+      </c>
+      <c r="AF18">
+        <v>1.73</v>
+      </c>
+      <c r="AG18">
+        <v>1.95</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["59", "64"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["15", "32", "39", "79"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>2.35</v>
       </c>
-      <c r="AD18">
-        <v>1.47</v>
-      </c>
-      <c r="AE18">
-        <v>1.15</v>
-      </c>
-      <c r="AF18">
-        <v>1.45</v>
-      </c>
-      <c r="AG18">
-        <v>2.63</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.23</v>
-      </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,36 +3383,36 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -3424,89 +3424,89 @@
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC19">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD19">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "38", "47", "88"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73", "90+3"]</t>
         </is>
       </c>
       <c r="AJ19">
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,139 +3537,139 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="AC20">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>2.53</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "54", "74"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3700,139 +3700,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q21">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
+        <v>1.33</v>
+      </c>
+      <c r="T21">
+        <v>3</v>
+      </c>
+      <c r="U21">
+        <v>2.75</v>
+      </c>
+      <c r="V21">
+        <v>1.4</v>
+      </c>
+      <c r="W21">
+        <v>1.08</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>1.29</v>
+      </c>
+      <c r="Z21">
+        <v>3.05</v>
+      </c>
+      <c r="AA21">
+        <v>1.92</v>
+      </c>
+      <c r="AB21">
+        <v>1.71</v>
+      </c>
+      <c r="AC21">
+        <v>3.3</v>
+      </c>
+      <c r="AD21">
+        <v>1.25</v>
+      </c>
+      <c r="AE21">
+        <v>1.08</v>
+      </c>
+      <c r="AF21">
+        <v>1.76</v>
+      </c>
+      <c r="AG21">
+        <v>1.85</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>["41", "67", "79", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>["10", "26"]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.25</v>
+      </c>
+      <c r="AK21">
+        <v>1.85</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>7</v>
+      </c>
+      <c r="AN21">
+        <v>5</v>
+      </c>
+      <c r="AO21">
+        <v>22</v>
+      </c>
+      <c r="AP21">
+        <v>10</v>
+      </c>
+      <c r="AQ21">
+        <v>2.23</v>
+      </c>
+      <c r="AR21">
         <v>1.3</v>
       </c>
-      <c r="T21">
-        <v>3.04</v>
-      </c>
-      <c r="U21">
-        <v>2.42</v>
-      </c>
-      <c r="V21">
-        <v>1.52</v>
-      </c>
-      <c r="W21">
-        <v>1.11</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>1.17</v>
-      </c>
-      <c r="Z21">
-        <v>3.98</v>
-      </c>
-      <c r="AA21">
-        <v>1.66</v>
-      </c>
-      <c r="AB21">
-        <v>2.16</v>
-      </c>
-      <c r="AC21">
-        <v>2.63</v>
-      </c>
-      <c r="AD21">
-        <v>1.41</v>
-      </c>
-      <c r="AE21">
-        <v>1.14</v>
-      </c>
-      <c r="AF21">
-        <v>1.62</v>
-      </c>
-      <c r="AG21">
-        <v>2.17</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.21</v>
-      </c>
-      <c r="AK21">
-        <v>1.87</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
       <c r="AS21">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3891,65 +3891,65 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T22">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U22">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V22">
         <v>1.29</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z22">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AA22">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB22">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC22">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
         <v>1.8</v>
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,39 +4047,39 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q23">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="R23">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
         <v>3.15</v>
       </c>
       <c r="U23">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
         <v>1.41</v>
@@ -4097,68 +4097,68 @@
         <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG23">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>["77"]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4221,49 +4221,49 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R24">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="S24">
         <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
         <v>2.97</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z24">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB24">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC24">
         <v>4</v>
@@ -4272,13 +4272,13 @@
         <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG24">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O25">
         <v>3.85</v>
@@ -4393,55 +4393,55 @@
         <v>4.05</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="R25">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V25">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE25">
         <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG25">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4524,51 +4524,51 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
         <v>11</v>
       </c>
       <c r="O26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T26">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
         <v>1.98</v>
@@ -4580,40 +4580,40 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB26">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AC26">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD26">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "58", "90+10"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "45+3", "50", "62", "75", "90+5"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.24</v>
+        <v>3.49</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q27">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T27">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W27">
         <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27">
         <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AC27">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="AD27">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O28">
-        <v>4.94</v>
+        <v>4.8</v>
       </c>
       <c r="P28">
-        <v>6.35</v>
+        <v>5.75</v>
       </c>
       <c r="Q28">
         <v>1.86</v>
       </c>
       <c r="R28">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V28">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W28">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,28 +4909,28 @@
         <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="AA28">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB28">
         <v>3</v>
       </c>
       <c r="AC28">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AD28">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE28">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>2.05</v>
@@ -5048,52 +5048,52 @@
         <v>3.75</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
         <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="U29">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AA29">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AK29">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="O30">
-        <v>6.6</v>
+        <v>5.75</v>
       </c>
       <c r="P30">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Q30">
-        <v>8.699999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="R30">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="U30">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="AA30">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB30">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AC30">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AD30">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE30">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG30">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>4.54</v>
+        <v>3.8</v>
       </c>
       <c r="AK30">
         <v>1.01</v>
@@ -5362,43 +5362,43 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
         <v>1.8</v>
@@ -5407,19 +5407,19 @@
         <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
         <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>3.44</v>
+        <v>3.86</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB32">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
         <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG32">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,61 +5688,61 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q33">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
         <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
         <v>2.05</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5875,40 +5875,40 @@
         <v>2.29</v>
       </c>
       <c r="V34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4</v>
+      </c>
+      <c r="AA34">
+        <v>1.67</v>
+      </c>
+      <c r="AB34">
+        <v>2.05</v>
+      </c>
+      <c r="AC34">
+        <v>2.38</v>
+      </c>
+      <c r="AD34">
+        <v>1.4</v>
+      </c>
+      <c r="AE34">
         <v>1.17</v>
       </c>
-      <c r="Z34">
-        <v>4.9</v>
-      </c>
-      <c r="AA34">
-        <v>1.52</v>
-      </c>
-      <c r="AB34">
-        <v>2.26</v>
-      </c>
-      <c r="AC34">
-        <v>2.28</v>
-      </c>
-      <c r="AD34">
-        <v>1.54</v>
-      </c>
-      <c r="AE34">
-        <v>1.18</v>
-      </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,58 +6020,58 @@
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="T35">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z35">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AA35">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB35">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD35">
         <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="O36">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="S36">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U36">
         <v>3</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z36">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB36">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC36">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R37">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S37">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="T37">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="U37">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="V37">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
+        <v>1.03</v>
+      </c>
+      <c r="X37">
         <v>1.05</v>
       </c>
-      <c r="X37">
-        <v>1.07</v>
-      </c>
       <c r="Y37">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z37">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="AA37">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AB37">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC37">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD37">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE37">
         <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG37">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="O38">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T38">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U38">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="V38">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y38">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z38">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AA38">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB38">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC38">
         <v>4.5</v>
       </c>
       <c r="AD38">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE38">
         <v>1.02</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK38">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.25</v>
+      </c>
+      <c r="O39">
+        <v>6.15</v>
+      </c>
+      <c r="P39">
+        <v>10.5</v>
+      </c>
+      <c r="Q39">
+        <v>1.67</v>
+      </c>
+      <c r="R39">
+        <v>2.56</v>
+      </c>
+      <c r="S39">
         <v>1.27</v>
       </c>
-      <c r="O39">
-        <v>5.3</v>
-      </c>
-      <c r="P39">
-        <v>8.5</v>
-      </c>
-      <c r="Q39">
-        <v>1.73</v>
-      </c>
-      <c r="R39">
+      <c r="T39">
+        <v>2.91</v>
+      </c>
+      <c r="U39">
+        <v>2.25</v>
+      </c>
+      <c r="V39">
+        <v>1.55</v>
+      </c>
+      <c r="W39">
+        <v>1.1</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4.2</v>
+      </c>
+      <c r="AA39">
+        <v>1.76</v>
+      </c>
+      <c r="AB39">
+        <v>2.06</v>
+      </c>
+      <c r="AC39">
         <v>2.45</v>
       </c>
-      <c r="S39">
-        <v>1.33</v>
-      </c>
-      <c r="T39">
-        <v>3.31</v>
-      </c>
-      <c r="U39">
-        <v>2.5</v>
-      </c>
-      <c r="V39">
+      <c r="AD39">
         <v>1.44</v>
       </c>
-      <c r="W39">
+      <c r="AE39">
+        <v>1.2</v>
+      </c>
+      <c r="AF39">
+        <v>2.1</v>
+      </c>
+      <c r="AG39">
+        <v>1.64</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.11</v>
       </c>
-      <c r="X39">
-        <v>1</v>
-      </c>
-      <c r="Y39">
-        <v>1.19</v>
-      </c>
-      <c r="Z39">
-        <v>3.76</v>
-      </c>
-      <c r="AA39">
-        <v>1.73</v>
-      </c>
-      <c r="AB39">
-        <v>2.07</v>
-      </c>
-      <c r="AC39">
-        <v>2.68</v>
-      </c>
-      <c r="AD39">
-        <v>1.41</v>
-      </c>
-      <c r="AE39">
-        <v>1.14</v>
-      </c>
-      <c r="AF39">
-        <v>2.15</v>
-      </c>
-      <c r="AG39">
-        <v>1.57</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.05</v>
-      </c>
       <c r="AK39">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
         <v>3.25</v>
       </c>
       <c r="Q40">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U40">
-        <v>3.09</v>
+        <v>2.71</v>
       </c>
       <c r="V40">
         <v>1.36</v>
@@ -6859,34 +6859,34 @@
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z40">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="AA40">
         <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
         <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>1.67</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.14</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>6.52</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>23.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>1.36</v>
+        <v>3.28</v>
       </c>
       <c r="R41">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="U41">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AB41">
-        <v>4</v>
+        <v>2.17</v>
       </c>
       <c r="AC41">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AD41">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE41">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AK41">
-        <v>6.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O42">
+        <v>3.5</v>
+      </c>
+      <c r="P42">
+        <v>4.1</v>
+      </c>
+      <c r="Q42">
+        <v>2.24</v>
+      </c>
+      <c r="R42">
+        <v>2.5</v>
+      </c>
+      <c r="S42">
+        <v>1.25</v>
+      </c>
+      <c r="T42">
         <v>4</v>
       </c>
-      <c r="P42">
-        <v>4.02</v>
-      </c>
-      <c r="Q42">
-        <v>2.34</v>
-      </c>
-      <c r="R42">
-        <v>2.26</v>
-      </c>
-      <c r="S42">
-        <v>1.22</v>
-      </c>
-      <c r="T42">
-        <v>3.6</v>
-      </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="V42">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA42">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB42">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AC42">
         <v>2.45</v>
       </c>
       <c r="AD42">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE42">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.14</v>
+      </c>
+      <c r="O43">
+        <v>6.52</v>
+      </c>
+      <c r="P43">
+        <v>23.56</v>
+      </c>
+      <c r="Q43">
+        <v>1.34</v>
+      </c>
+      <c r="R43">
+        <v>3.65</v>
+      </c>
+      <c r="S43">
         <v>1.13</v>
       </c>
-      <c r="O43">
-        <v>11</v>
-      </c>
-      <c r="P43">
-        <v>20</v>
-      </c>
-      <c r="Q43">
-        <v>1.31</v>
-      </c>
-      <c r="R43">
-        <v>4.4</v>
-      </c>
-      <c r="S43">
-        <v>1.05</v>
-      </c>
       <c r="T43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="V43">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="W43">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z43">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AA43">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AB43">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AC43">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AE43">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AF43">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG43">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK43">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.4</v>
+        <v>1.11</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>20</v>
       </c>
       <c r="Q44">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="S44">
+        <v>1.08</v>
+      </c>
+      <c r="T44">
+        <v>7</v>
+      </c>
+      <c r="U44">
+        <v>1.5</v>
+      </c>
+      <c r="V44">
+        <v>2.71</v>
+      </c>
+      <c r="W44">
+        <v>1.51</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.02</v>
+      </c>
+      <c r="Z44">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA44">
+        <v>1.07</v>
+      </c>
+      <c r="AB44">
+        <v>5.75</v>
+      </c>
+      <c r="AC44">
         <v>1.3</v>
       </c>
-      <c r="T44">
-        <v>3.15</v>
-      </c>
-      <c r="U44">
-        <v>2.57</v>
-      </c>
-      <c r="V44">
-        <v>1.5</v>
-      </c>
-      <c r="W44">
-        <v>1.08</v>
-      </c>
-      <c r="X44">
-        <v>1.05</v>
-      </c>
-      <c r="Y44">
-        <v>1.22</v>
-      </c>
-      <c r="Z44">
-        <v>4</v>
-      </c>
-      <c r="AA44">
-        <v>1.75</v>
-      </c>
-      <c r="AB44">
-        <v>2.05</v>
-      </c>
-      <c r="AC44">
-        <v>2.9</v>
-      </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AE44">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,37 +7644,37 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="O45">
         <v>3.3</v>
       </c>
       <c r="P45">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R45">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
         <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U45">
         <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W45">
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
         <v>1.25</v>
@@ -7683,19 +7683,19 @@
         <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB45">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC45">
         <v>3.2</v>
       </c>
       <c r="AD45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
         <v>1.67</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AK45">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,37 +7807,37 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.84</v>
+        <v>5.9</v>
       </c>
       <c r="O46">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="P46">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q46">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="R46">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T46">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="U46">
         <v>2.65</v>
       </c>
       <c r="V46">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
         <v>1.29</v>
@@ -7846,19 +7846,19 @@
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB46">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC46">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD46">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
         <v>1.83</v>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
         <v>7</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="R47">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="S47">
         <v>1.44</v>
@@ -7991,43 +7991,43 @@
         <v>2.63</v>
       </c>
       <c r="U47">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="V47">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
         <v>1.04</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y47">
         <v>1.4</v>
       </c>
       <c r="Z47">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA47">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="AB47">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AC47">
-        <v>4.15</v>
+        <v>5.05</v>
       </c>
       <c r="AD47">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE47">
         <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AG47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R48">
         <v>2.1</v>
@@ -8151,31 +8151,31 @@
         <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W48">
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA48">
         <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC48">
         <v>3.8</v>
@@ -8184,13 +8184,13 @@
         <v>1.22</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG48">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P49">
         <v>3.7</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R49">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="S49">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T49">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U49">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="V49">
         <v>1.25</v>
       </c>
       <c r="W49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
         <v>1.11</v>
@@ -8332,28 +8332,28 @@
         <v>1.5</v>
       </c>
       <c r="Z49">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="AA49">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="AB49">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC49">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AD49">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG49">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>11.04</v>
       </c>
       <c r="Q51">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R51">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U51">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V51">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
         <v>1.17</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC51">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD51">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE51">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG51">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.08</v>
       </c>
       <c r="AK51">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AL51">
         <v>0</v>
